--- a/research/traditional_assets/database/data/italy/italy_paper_forest_products.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_paper_forest_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09412938365360399</v>
+        <v>0.09393767313283535</v>
       </c>
       <c r="C2">
-        <v>91.08334267120304</v>
+        <v>90.34964290580228</v>
       </c>
       <c r="D2">
-        <v>82.94334267120304</v>
+        <v>83.12864290580228</v>
       </c>
       <c r="E2">
-        <v>-51.8</v>
+        <v>-50.88100000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.919</v>
       </c>
       <c r="G2">
         <v>8.140000000000001</v>
@@ -1451,28 +1451,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0462257</v>
       </c>
       <c r="N2">
-        <v>9.466666666666665</v>
+        <v>9.420440966666664</v>
       </c>
       <c r="O2">
-        <v>2.271999999999999</v>
+        <v>2.260905831999999</v>
       </c>
       <c r="P2">
-        <v>7.194666666666666</v>
+        <v>7.159535134666665</v>
       </c>
       <c r="Q2">
-        <v>17.19466666666667</v>
+        <v>17.15953513466667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09412938365360399</v>
+        <v>0.09450039710387409</v>
       </c>
       <c r="T2">
-        <v>0.6652721574126821</v>
+        <v>0.6703792972069613</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>204.7922836575036</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09393767313283535</v>
+        <v>0.09374596261206669</v>
       </c>
       <c r="C3">
-        <v>90.34964290580228</v>
+        <v>89.61677293714231</v>
       </c>
       <c r="D3">
-        <v>83.12864290580228</v>
+        <v>83.31477293714231</v>
       </c>
       <c r="E3">
-        <v>-50.88100000000001</v>
+        <v>-49.962</v>
       </c>
       <c r="F3">
-        <v>0.919</v>
+        <v>1.838</v>
       </c>
       <c r="G3">
         <v>8.140000000000001</v>
@@ -1533,28 +1533,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M3">
-        <v>0.0462257</v>
+        <v>0.0924514</v>
       </c>
       <c r="N3">
-        <v>9.420440966666664</v>
+        <v>9.374215266666665</v>
       </c>
       <c r="O3">
-        <v>2.260905831999999</v>
+        <v>2.249811664</v>
       </c>
       <c r="P3">
-        <v>7.159535134666665</v>
+        <v>7.124403602666666</v>
       </c>
       <c r="Q3">
-        <v>17.15953513466667</v>
+        <v>17.12440360266667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09450039710387409</v>
+        <v>0.09487898225721092</v>
       </c>
       <c r="T3">
-        <v>0.6703792972069613</v>
+        <v>0.6755906643439809</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>204.7922836575036</v>
+        <v>102.3961418287518</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09374596261206669</v>
+        <v>0.09355425209129804</v>
       </c>
       <c r="C4">
-        <v>89.61677293714231</v>
+        <v>88.88473835162581</v>
       </c>
       <c r="D4">
-        <v>83.31477293714231</v>
+        <v>83.50173835162582</v>
       </c>
       <c r="E4">
-        <v>-49.962</v>
+        <v>-49.04300000000001</v>
       </c>
       <c r="F4">
-        <v>1.838</v>
+        <v>2.757</v>
       </c>
       <c r="G4">
         <v>8.140000000000001</v>
@@ -1615,28 +1615,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M4">
-        <v>0.0924514</v>
+        <v>0.1386771</v>
       </c>
       <c r="N4">
-        <v>9.374215266666665</v>
+        <v>9.327989566666664</v>
       </c>
       <c r="O4">
-        <v>2.249811664</v>
+        <v>2.238717495999999</v>
       </c>
       <c r="P4">
-        <v>7.124403602666666</v>
+        <v>7.089272070666665</v>
       </c>
       <c r="Q4">
-        <v>17.12440360266667</v>
+        <v>17.08927207066667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09487898225721092</v>
+        <v>0.09526537328999798</v>
       </c>
       <c r="T4">
-        <v>0.6755906643439809</v>
+        <v>0.680909482349805</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>102.3961418287518</v>
+        <v>68.26409455250121</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09355425209129804</v>
+        <v>0.09336254157052938</v>
       </c>
       <c r="C5">
-        <v>88.88473835162581</v>
+        <v>88.15354478591377</v>
       </c>
       <c r="D5">
-        <v>83.50173835162582</v>
+        <v>83.68954478591377</v>
       </c>
       <c r="E5">
-        <v>-49.04300000000001</v>
+        <v>-48.124</v>
       </c>
       <c r="F5">
-        <v>2.757</v>
+        <v>3.676</v>
       </c>
       <c r="G5">
         <v>8.140000000000001</v>
@@ -1697,28 +1697,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M5">
-        <v>0.1386771</v>
+        <v>0.1849028</v>
       </c>
       <c r="N5">
-        <v>9.327989566666664</v>
+        <v>9.281763866666665</v>
       </c>
       <c r="O5">
-        <v>2.238717495999999</v>
+        <v>2.227623328</v>
       </c>
       <c r="P5">
-        <v>7.089272070666665</v>
+        <v>7.054140538666665</v>
       </c>
       <c r="Q5">
-        <v>17.08927207066667</v>
+        <v>17.05414053866667</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09526537328999798</v>
+        <v>0.09565981413596811</v>
       </c>
       <c r="T5">
-        <v>0.680909482349805</v>
+        <v>0.6863391090640837</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>68.26409455250121</v>
+        <v>51.1980709143759</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09336254157052938</v>
+        <v>0.09317083104976073</v>
       </c>
       <c r="C6">
-        <v>88.15354478591377</v>
+        <v>87.42319792749177</v>
       </c>
       <c r="D6">
-        <v>83.68954478591377</v>
+        <v>83.87819792749177</v>
       </c>
       <c r="E6">
-        <v>-48.124</v>
+        <v>-47.20500000000001</v>
       </c>
       <c r="F6">
-        <v>3.676</v>
+        <v>4.595000000000001</v>
       </c>
       <c r="G6">
         <v>8.140000000000001</v>
@@ -1779,28 +1779,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M6">
-        <v>0.1849028</v>
+        <v>0.2311285</v>
       </c>
       <c r="N6">
-        <v>9.281763866666665</v>
+        <v>9.235538166666664</v>
       </c>
       <c r="O6">
-        <v>2.227623328</v>
+        <v>2.216529159999999</v>
       </c>
       <c r="P6">
-        <v>7.054140538666665</v>
+        <v>7.019009006666665</v>
       </c>
       <c r="Q6">
-        <v>17.05414053866667</v>
+        <v>17.01900900666666</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09565981413596811</v>
+        <v>0.09606255899974815</v>
       </c>
       <c r="T6">
-        <v>0.6863391090640837</v>
+        <v>0.6918830437091894</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>51.1980709143759</v>
+        <v>40.95845673150072</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09317083104976073</v>
+        <v>0.09297912052899208</v>
       </c>
       <c r="C7">
-        <v>87.42319792749177</v>
+        <v>86.69370351524435</v>
       </c>
       <c r="D7">
-        <v>83.87819792749177</v>
+        <v>84.06770351524435</v>
       </c>
       <c r="E7">
-        <v>-47.20500000000001</v>
+        <v>-46.286</v>
       </c>
       <c r="F7">
-        <v>4.595000000000001</v>
+        <v>5.514000000000001</v>
       </c>
       <c r="G7">
         <v>8.140000000000001</v>
@@ -1861,28 +1861,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M7">
-        <v>0.2311285</v>
+        <v>0.2773542000000001</v>
       </c>
       <c r="N7">
-        <v>9.235538166666664</v>
+        <v>9.189312466666665</v>
       </c>
       <c r="O7">
-        <v>2.216529159999999</v>
+        <v>2.205434992</v>
       </c>
       <c r="P7">
-        <v>7.019009006666665</v>
+        <v>6.983877474666666</v>
       </c>
       <c r="Q7">
-        <v>17.01900900666666</v>
+        <v>16.98387747466667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09606255899974815</v>
+        <v>0.09647387290318307</v>
       </c>
       <c r="T7">
-        <v>0.6918830437091894</v>
+        <v>0.697544934410574</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.95845673150072</v>
+        <v>34.1320472762506</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09297912052899208</v>
+        <v>0.09278741000822345</v>
       </c>
       <c r="C8">
-        <v>86.69370351524435</v>
+        <v>85.96506734003674</v>
       </c>
       <c r="D8">
-        <v>84.06770351524435</v>
+        <v>84.25806734003673</v>
       </c>
       <c r="E8">
-        <v>-46.286</v>
+        <v>-45.367</v>
       </c>
       <c r="F8">
-        <v>5.514</v>
+        <v>6.433</v>
       </c>
       <c r="G8">
         <v>8.140000000000001</v>
@@ -1943,28 +1943,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M8">
-        <v>0.2773542</v>
+        <v>0.3235799</v>
       </c>
       <c r="N8">
-        <v>9.189312466666665</v>
+        <v>9.143086766666665</v>
       </c>
       <c r="O8">
-        <v>2.205434992</v>
+        <v>2.194340823999999</v>
       </c>
       <c r="P8">
-        <v>6.983877474666666</v>
+        <v>6.948745942666665</v>
       </c>
       <c r="Q8">
-        <v>16.98387747466667</v>
+        <v>16.94874594266667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09647387290318307</v>
+        <v>0.09689403226690693</v>
       </c>
       <c r="T8">
-        <v>0.697544934410574</v>
+        <v>0.7033285862023108</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.1320472762506</v>
+        <v>29.25604052250052</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09278741000822345</v>
+        <v>0.09259569948745479</v>
       </c>
       <c r="C9">
-        <v>85.96506734003673</v>
+        <v>85.23729524530481</v>
       </c>
       <c r="D9">
-        <v>84.25806734003673</v>
+        <v>84.44929524530481</v>
       </c>
       <c r="E9">
-        <v>-45.367</v>
+        <v>-44.44800000000001</v>
       </c>
       <c r="F9">
-        <v>6.433000000000001</v>
+        <v>7.352</v>
       </c>
       <c r="G9">
         <v>8.140000000000001</v>
@@ -2025,28 +2025,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M9">
-        <v>0.3235799</v>
+        <v>0.3698056</v>
       </c>
       <c r="N9">
-        <v>9.143086766666665</v>
+        <v>9.096861066666666</v>
       </c>
       <c r="O9">
-        <v>2.194340823999999</v>
+        <v>2.183246656</v>
       </c>
       <c r="P9">
-        <v>6.948745942666665</v>
+        <v>6.913614410666666</v>
       </c>
       <c r="Q9">
-        <v>16.94874594266667</v>
+        <v>16.91361441066667</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09689403226690693</v>
+        <v>0.09732332552984216</v>
       </c>
       <c r="T9">
-        <v>0.7033285862023108</v>
+        <v>0.7092379695547375</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.25604052250051</v>
+        <v>25.59903545718795</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09259569948745479</v>
+        <v>0.09240398896668614</v>
       </c>
       <c r="C10">
-        <v>85.23729524530481</v>
+        <v>84.510393127653</v>
       </c>
       <c r="D10">
-        <v>84.44929524530481</v>
+        <v>84.641393127653</v>
       </c>
       <c r="E10">
-        <v>-44.44800000000001</v>
+        <v>-43.529</v>
       </c>
       <c r="F10">
-        <v>7.352</v>
+        <v>8.271000000000001</v>
       </c>
       <c r="G10">
         <v>8.140000000000001</v>
@@ -2107,28 +2107,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M10">
-        <v>0.3698056</v>
+        <v>0.4160313</v>
       </c>
       <c r="N10">
-        <v>9.096861066666666</v>
+        <v>9.050635366666665</v>
       </c>
       <c r="O10">
-        <v>2.183246656</v>
+        <v>2.172152488</v>
       </c>
       <c r="P10">
-        <v>6.913614410666666</v>
+        <v>6.878482878666665</v>
       </c>
       <c r="Q10">
-        <v>16.91361441066667</v>
+        <v>16.87848287866667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09732332552984216</v>
+        <v>0.09776205380954521</v>
       </c>
       <c r="T10">
-        <v>0.7092379695547375</v>
+        <v>0.7152772294643606</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.59903545718795</v>
+        <v>22.75469818416707</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09240398896668614</v>
+        <v>0.09221227844591751</v>
       </c>
       <c r="C11">
-        <v>84.510393127653</v>
+        <v>83.78436693746039</v>
       </c>
       <c r="D11">
-        <v>84.641393127653</v>
+        <v>84.83436693746039</v>
       </c>
       <c r="E11">
-        <v>-43.529</v>
+        <v>-42.61000000000001</v>
       </c>
       <c r="F11">
-        <v>8.271000000000001</v>
+        <v>9.19</v>
       </c>
       <c r="G11">
         <v>8.140000000000001</v>
@@ -2189,28 +2189,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M11">
-        <v>0.4160313</v>
+        <v>0.462257</v>
       </c>
       <c r="N11">
-        <v>9.050635366666665</v>
+        <v>9.004409666666666</v>
       </c>
       <c r="O11">
-        <v>2.172152488</v>
+        <v>2.16105832</v>
       </c>
       <c r="P11">
-        <v>6.878482878666665</v>
+        <v>6.843351346666666</v>
       </c>
       <c r="Q11">
-        <v>16.87848287866667</v>
+        <v>16.84335134666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09776205380954521</v>
+        <v>0.098210531606575</v>
       </c>
       <c r="T11">
-        <v>0.7152772294643606</v>
+        <v>0.7214506951497531</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.75469818416707</v>
+        <v>20.47922836575037</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09221227844591751</v>
+        <v>0.09202056792514884</v>
       </c>
       <c r="C12">
-        <v>83.78436693746039</v>
+        <v>83.05922267949512</v>
       </c>
       <c r="D12">
-        <v>84.83436693746039</v>
+        <v>85.02822267949512</v>
       </c>
       <c r="E12">
-        <v>-42.61</v>
+        <v>-41.691</v>
       </c>
       <c r="F12">
-        <v>9.190000000000001</v>
+        <v>10.109</v>
       </c>
       <c r="G12">
         <v>8.140000000000001</v>
@@ -2271,28 +2271,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M12">
-        <v>0.462257</v>
+        <v>0.5084827</v>
       </c>
       <c r="N12">
-        <v>9.004409666666666</v>
+        <v>8.958183966666665</v>
       </c>
       <c r="O12">
-        <v>2.16105832</v>
+        <v>2.149964151999999</v>
       </c>
       <c r="P12">
-        <v>6.843351346666666</v>
+        <v>6.808219814666666</v>
       </c>
       <c r="Q12">
-        <v>16.84335134666667</v>
+        <v>16.80821981466666</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.098210531606575</v>
+        <v>0.09866908755634701</v>
       </c>
       <c r="T12">
-        <v>0.7214506951497531</v>
+        <v>0.7277628904011093</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.47922836575036</v>
+        <v>18.61748033250033</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09202056792514884</v>
+        <v>0.0918288574043802</v>
       </c>
       <c r="C13">
-        <v>83.05922267949512</v>
+        <v>82.33496641353719</v>
       </c>
       <c r="D13">
-        <v>85.02822267949512</v>
+        <v>85.22296641353719</v>
       </c>
       <c r="E13">
-        <v>-41.691</v>
+        <v>-40.77200000000001</v>
       </c>
       <c r="F13">
-        <v>10.109</v>
+        <v>11.028</v>
       </c>
       <c r="G13">
         <v>8.140000000000001</v>
@@ -2353,28 +2353,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M13">
-        <v>0.5084827</v>
+        <v>0.5547084</v>
       </c>
       <c r="N13">
-        <v>8.958183966666665</v>
+        <v>8.911958266666666</v>
       </c>
       <c r="O13">
-        <v>2.149964151999999</v>
+        <v>2.138869984</v>
       </c>
       <c r="P13">
-        <v>6.808219814666666</v>
+        <v>6.773088282666667</v>
       </c>
       <c r="Q13">
-        <v>16.80821981466666</v>
+        <v>16.77308828266667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09866908755634701</v>
+        <v>0.09913806523225022</v>
       </c>
       <c r="T13">
-        <v>0.7277628904011093</v>
+        <v>0.7342185446354509</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.61748033250033</v>
+        <v>17.0660236381253</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0918288574043802</v>
+        <v>0.09163714688361155</v>
       </c>
       <c r="C14">
-        <v>82.33496641353719</v>
+        <v>81.61160425500994</v>
       </c>
       <c r="D14">
-        <v>85.22296641353719</v>
+        <v>85.41860425500994</v>
       </c>
       <c r="E14">
-        <v>-40.77200000000001</v>
+        <v>-39.853</v>
       </c>
       <c r="F14">
-        <v>11.028</v>
+        <v>11.947</v>
       </c>
       <c r="G14">
         <v>8.140000000000001</v>
@@ -2435,28 +2435,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M14">
-        <v>0.5547084</v>
+        <v>0.6009341</v>
       </c>
       <c r="N14">
-        <v>8.911958266666666</v>
+        <v>8.865732566666665</v>
       </c>
       <c r="O14">
-        <v>2.138869984</v>
+        <v>2.127775816</v>
       </c>
       <c r="P14">
-        <v>6.773088282666667</v>
+        <v>6.737956750666665</v>
       </c>
       <c r="Q14">
-        <v>16.77308828266667</v>
+        <v>16.73795675066667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09913806523225022</v>
+        <v>0.0996178240041512</v>
       </c>
       <c r="T14">
-        <v>0.7342185446354509</v>
+        <v>0.7408226047142603</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.0660236381253</v>
+        <v>15.75325258903874</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09163714688361155</v>
+        <v>0.09144543636284289</v>
       </c>
       <c r="C15">
-        <v>81.61160425500994</v>
+        <v>80.88914237562027</v>
       </c>
       <c r="D15">
-        <v>85.41860425500994</v>
+        <v>85.61514237562027</v>
       </c>
       <c r="E15">
-        <v>-39.853</v>
+        <v>-38.934</v>
       </c>
       <c r="F15">
-        <v>11.947</v>
+        <v>12.866</v>
       </c>
       <c r="G15">
         <v>8.140000000000001</v>
@@ -2517,28 +2517,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M15">
-        <v>0.6009341</v>
+        <v>0.6471598000000001</v>
       </c>
       <c r="N15">
-        <v>8.865732566666665</v>
+        <v>8.819506866666664</v>
       </c>
       <c r="O15">
-        <v>2.127775816</v>
+        <v>2.116681647999999</v>
       </c>
       <c r="P15">
-        <v>6.737956750666665</v>
+        <v>6.702825218666665</v>
       </c>
       <c r="Q15">
-        <v>16.73795675066667</v>
+        <v>16.70282521866666</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0996178240041512</v>
+        <v>0.1001087399567941</v>
       </c>
       <c r="T15">
-        <v>0.7408226047142603</v>
+        <v>0.7475802475855999</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.75325258903874</v>
+        <v>14.62802026125026</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09144543636284289</v>
+        <v>0.09125372584207425</v>
       </c>
       <c r="C16">
-        <v>80.88914237562027</v>
+        <v>80.16758700400732</v>
       </c>
       <c r="D16">
-        <v>85.61514237562027</v>
+        <v>85.81258700400733</v>
       </c>
       <c r="E16">
-        <v>-38.934</v>
+        <v>-38.015</v>
       </c>
       <c r="F16">
-        <v>12.866</v>
+        <v>13.785</v>
       </c>
       <c r="G16">
         <v>8.140000000000001</v>
@@ -2599,28 +2599,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M16">
-        <v>0.6471598000000001</v>
+        <v>0.6933855000000001</v>
       </c>
       <c r="N16">
-        <v>8.819506866666664</v>
+        <v>8.773281166666665</v>
       </c>
       <c r="O16">
-        <v>2.116681647999999</v>
+        <v>2.10558748</v>
       </c>
       <c r="P16">
-        <v>6.702825218666665</v>
+        <v>6.667693686666666</v>
       </c>
       <c r="Q16">
-        <v>16.70282521866666</v>
+        <v>16.66769368666667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1001087399567941</v>
+        <v>0.1006112068730285</v>
       </c>
       <c r="T16">
-        <v>0.7475802475855999</v>
+        <v>0.7544968938186184</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.62802026125026</v>
+        <v>13.65281891050024</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09125372584207424</v>
+        <v>0.09124441532130559</v>
       </c>
       <c r="C17">
-        <v>80.16758700400734</v>
+        <v>79.25819919530048</v>
       </c>
       <c r="D17">
-        <v>85.81258700400734</v>
+        <v>85.82219919530048</v>
       </c>
       <c r="E17">
-        <v>-38.015</v>
+        <v>-37.096</v>
       </c>
       <c r="F17">
-        <v>13.785</v>
+        <v>14.704</v>
       </c>
       <c r="G17">
         <v>8.140000000000001</v>
@@ -2681,45 +2681,45 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M17">
-        <v>0.6933855</v>
+        <v>0.7616672</v>
       </c>
       <c r="N17">
-        <v>8.773281166666665</v>
+        <v>8.704999466666665</v>
       </c>
       <c r="O17">
-        <v>2.10558748</v>
+        <v>2.089199872</v>
       </c>
       <c r="P17">
-        <v>6.667693686666666</v>
+        <v>6.615799594666665</v>
       </c>
       <c r="Q17">
-        <v>16.66769368666667</v>
+        <v>16.61579959466667</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1006112068730285</v>
+        <v>0.1011256372872686</v>
       </c>
       <c r="T17">
-        <v>0.7544968938186182</v>
+        <v>0.7615782221048037</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.24</v>
       </c>
       <c r="W17">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.65281891050024</v>
+        <v>12.42887532332581</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09124441532130559</v>
+        <v>0.09106410480053695</v>
       </c>
       <c r="C18">
-        <v>79.25819919530048</v>
+        <v>78.52577755893925</v>
       </c>
       <c r="D18">
-        <v>85.82219919530048</v>
+        <v>86.00877755893926</v>
       </c>
       <c r="E18">
-        <v>-37.096</v>
+        <v>-36.177</v>
       </c>
       <c r="F18">
-        <v>14.704</v>
+        <v>15.623</v>
       </c>
       <c r="G18">
         <v>8.140000000000001</v>
@@ -2763,28 +2763,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M18">
-        <v>0.7616672</v>
+        <v>0.8092714000000001</v>
       </c>
       <c r="N18">
-        <v>8.704999466666665</v>
+        <v>8.657395266666665</v>
       </c>
       <c r="O18">
-        <v>2.089199872</v>
+        <v>2.077774863999999</v>
       </c>
       <c r="P18">
-        <v>6.615799594666665</v>
+        <v>6.579620402666666</v>
       </c>
       <c r="Q18">
-        <v>16.61579959466667</v>
+        <v>16.57962040266667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1011256372872686</v>
+        <v>0.1016524636151048</v>
       </c>
       <c r="T18">
-        <v>0.7615782221048037</v>
+        <v>0.7688301848075237</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.42887532332581</v>
+        <v>11.697765010189</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09106410480053695</v>
+        <v>0.09088379427976831</v>
       </c>
       <c r="C19">
-        <v>78.52577755893925</v>
+        <v>77.79416893672892</v>
       </c>
       <c r="D19">
-        <v>86.00877755893926</v>
+        <v>86.19616893672892</v>
       </c>
       <c r="E19">
-        <v>-36.177</v>
+        <v>-35.258</v>
       </c>
       <c r="F19">
-        <v>15.623</v>
+        <v>16.542</v>
       </c>
       <c r="G19">
         <v>8.140000000000001</v>
@@ -2845,28 +2845,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M19">
-        <v>0.8092714000000001</v>
+        <v>0.8568756000000001</v>
       </c>
       <c r="N19">
-        <v>8.657395266666665</v>
+        <v>8.609791066666665</v>
       </c>
       <c r="O19">
-        <v>2.077774863999999</v>
+        <v>2.066349856</v>
       </c>
       <c r="P19">
-        <v>6.579620402666666</v>
+        <v>6.543441210666665</v>
       </c>
       <c r="Q19">
-        <v>16.57962040266667</v>
+        <v>16.54344121066666</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1016524636151048</v>
+        <v>0.1021921393655711</v>
       </c>
       <c r="T19">
-        <v>0.7688301848075237</v>
+        <v>0.7762590246493345</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.697765010189</v>
+        <v>11.04788917628961</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.0908837942797683</v>
+        <v>0.09070348375899966</v>
       </c>
       <c r="C20">
-        <v>77.79416893672895</v>
+        <v>77.06337865432954</v>
       </c>
       <c r="D20">
-        <v>86.19616893672895</v>
+        <v>86.38437865432954</v>
       </c>
       <c r="E20">
-        <v>-35.258</v>
+        <v>-34.339</v>
       </c>
       <c r="F20">
-        <v>16.542</v>
+        <v>17.461</v>
       </c>
       <c r="G20">
         <v>8.140000000000001</v>
@@ -2927,28 +2927,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M20">
-        <v>0.8568756000000001</v>
+        <v>0.9044798000000001</v>
       </c>
       <c r="N20">
-        <v>8.609791066666665</v>
+        <v>8.562186866666664</v>
       </c>
       <c r="O20">
-        <v>2.066349856</v>
+        <v>2.054924847999999</v>
       </c>
       <c r="P20">
-        <v>6.543441210666665</v>
+        <v>6.507262018666665</v>
       </c>
       <c r="Q20">
-        <v>16.54344121066666</v>
+        <v>16.50726201866667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1021921393655711</v>
+        <v>0.1027451404432094</v>
       </c>
       <c r="T20">
-        <v>0.7762590246493344</v>
+        <v>0.7838712926353874</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.04788917628961</v>
+        <v>10.46642132490594</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09070348375899966</v>
+        <v>0.090523173238231</v>
       </c>
       <c r="C21">
-        <v>77.06337865432954</v>
+        <v>76.33341208401728</v>
       </c>
       <c r="D21">
-        <v>86.38437865432954</v>
+        <v>86.57341208401728</v>
       </c>
       <c r="E21">
-        <v>-34.339</v>
+        <v>-33.42</v>
       </c>
       <c r="F21">
-        <v>17.461</v>
+        <v>18.38</v>
       </c>
       <c r="G21">
         <v>8.140000000000001</v>
@@ -3009,28 +3009,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M21">
-        <v>0.9044798000000001</v>
+        <v>0.9520840000000002</v>
       </c>
       <c r="N21">
-        <v>8.562186866666664</v>
+        <v>8.514582666666666</v>
       </c>
       <c r="O21">
-        <v>2.054924847999999</v>
+        <v>2.04349984</v>
       </c>
       <c r="P21">
-        <v>6.507262018666665</v>
+        <v>6.471082826666667</v>
       </c>
       <c r="Q21">
-        <v>16.50726201866667</v>
+        <v>16.47108282666667</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1027451404432094</v>
+        <v>0.1033119665477887</v>
       </c>
       <c r="T21">
-        <v>0.7838712926353874</v>
+        <v>0.7916738673210917</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.46642132490594</v>
+        <v>9.943100258660648</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.090523173238231</v>
+        <v>0.09061418271746235</v>
       </c>
       <c r="C22">
-        <v>76.33341208401728</v>
+        <v>75.31889653438452</v>
       </c>
       <c r="D22">
-        <v>86.57341208401728</v>
+        <v>86.47789653438453</v>
       </c>
       <c r="E22">
-        <v>-33.42</v>
+        <v>-32.501</v>
       </c>
       <c r="F22">
-        <v>18.38</v>
+        <v>19.299</v>
       </c>
       <c r="G22">
         <v>8.140000000000001</v>
@@ -3091,45 +3091,45 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M22">
-        <v>0.9520840000000002</v>
+        <v>1.0324965</v>
       </c>
       <c r="N22">
-        <v>8.514582666666666</v>
+        <v>8.434170166666664</v>
       </c>
       <c r="O22">
-        <v>2.04349984</v>
+        <v>2.024200839999999</v>
       </c>
       <c r="P22">
-        <v>6.471082826666667</v>
+        <v>6.409969326666666</v>
       </c>
       <c r="Q22">
-        <v>16.47108282666667</v>
+        <v>16.40996932666667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1033119665477887</v>
+        <v>0.1038931426803321</v>
       </c>
       <c r="T22">
-        <v>0.7916738673210917</v>
+        <v>0.7996739755431429</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.24</v>
       </c>
       <c r="W22">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>9.943100258660648</v>
+        <v>9.168715503313244</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09061418271746235</v>
+        <v>0.0904467921966937</v>
       </c>
       <c r="C23">
-        <v>75.31889653438452</v>
+        <v>74.57573791181009</v>
       </c>
       <c r="D23">
-        <v>86.47789653438453</v>
+        <v>86.6537379118101</v>
       </c>
       <c r="E23">
-        <v>-32.501</v>
+        <v>-31.582</v>
       </c>
       <c r="F23">
-        <v>19.299</v>
+        <v>20.218</v>
       </c>
       <c r="G23">
         <v>8.140000000000001</v>
@@ -3173,28 +3173,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M23">
-        <v>1.0324965</v>
+        <v>1.081663</v>
       </c>
       <c r="N23">
-        <v>8.434170166666664</v>
+        <v>8.385003666666664</v>
       </c>
       <c r="O23">
-        <v>2.024200839999999</v>
+        <v>2.01240088</v>
       </c>
       <c r="P23">
-        <v>6.409969326666666</v>
+        <v>6.372602786666665</v>
       </c>
       <c r="Q23">
-        <v>16.40996932666667</v>
+        <v>16.37260278666666</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1038931426803321</v>
+        <v>0.1044892207649919</v>
       </c>
       <c r="T23">
-        <v>0.7996739755431429</v>
+        <v>0.8078792147452468</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.168715503313246</v>
+        <v>8.751955707708097</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0904467921966937</v>
+        <v>0.09027940167592508</v>
       </c>
       <c r="C24">
-        <v>74.57573791181009</v>
+        <v>73.83329584667935</v>
       </c>
       <c r="D24">
-        <v>86.6537379118101</v>
+        <v>86.83029584667935</v>
       </c>
       <c r="E24">
-        <v>-31.582</v>
+        <v>-30.663</v>
       </c>
       <c r="F24">
-        <v>20.218</v>
+        <v>21.137</v>
       </c>
       <c r="G24">
         <v>8.140000000000001</v>
@@ -3255,28 +3255,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M24">
-        <v>1.081663</v>
+        <v>1.1308295</v>
       </c>
       <c r="N24">
-        <v>8.385003666666664</v>
+        <v>8.335837166666664</v>
       </c>
       <c r="O24">
-        <v>2.01240088</v>
+        <v>2.000600919999999</v>
       </c>
       <c r="P24">
-        <v>6.372602786666665</v>
+        <v>6.335236246666665</v>
       </c>
       <c r="Q24">
-        <v>16.37260278666666</v>
+        <v>16.33523624666666</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1044892207649919</v>
+        <v>0.1051007813973053</v>
       </c>
       <c r="T24">
-        <v>0.8078792147452468</v>
+        <v>0.8162975770435092</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.751955707708097</v>
+        <v>8.371435894329485</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09027940167592508</v>
+        <v>0.09011201115515639</v>
       </c>
       <c r="C25">
-        <v>73.83329584667935</v>
+        <v>73.09157472791566</v>
       </c>
       <c r="D25">
-        <v>86.83029584667935</v>
+        <v>87.00757472791565</v>
       </c>
       <c r="E25">
-        <v>-30.663</v>
+        <v>-29.744</v>
       </c>
       <c r="F25">
-        <v>21.137</v>
+        <v>22.056</v>
       </c>
       <c r="G25">
         <v>8.140000000000001</v>
@@ -3337,28 +3337,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M25">
-        <v>1.1308295</v>
+        <v>1.179996</v>
       </c>
       <c r="N25">
-        <v>8.335837166666664</v>
+        <v>8.286670666666664</v>
       </c>
       <c r="O25">
-        <v>2.000600919999999</v>
+        <v>1.988800959999999</v>
       </c>
       <c r="P25">
-        <v>6.335236246666665</v>
+        <v>6.297869706666665</v>
       </c>
       <c r="Q25">
-        <v>16.33523624666666</v>
+        <v>16.29786970666667</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1051007813973053</v>
+        <v>0.1057284357304689</v>
       </c>
       <c r="T25">
-        <v>0.8162975770435092</v>
+        <v>0.8249374751917258</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.371435894329485</v>
+        <v>8.022626065399088</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09011201115515639</v>
+        <v>0.08994462063438777</v>
       </c>
       <c r="C26">
-        <v>73.09157472791566</v>
+        <v>72.35057898035839</v>
       </c>
       <c r="D26">
-        <v>87.00757472791565</v>
+        <v>87.1855789803584</v>
       </c>
       <c r="E26">
-        <v>-29.744</v>
+        <v>-28.825</v>
       </c>
       <c r="F26">
-        <v>22.056</v>
+        <v>22.975</v>
       </c>
       <c r="G26">
         <v>8.140000000000001</v>
@@ -3419,28 +3419,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M26">
-        <v>1.179996</v>
+        <v>1.2291625</v>
       </c>
       <c r="N26">
-        <v>8.286670666666666</v>
+        <v>8.237504166666664</v>
       </c>
       <c r="O26">
-        <v>1.98880096</v>
+        <v>1.977000999999999</v>
       </c>
       <c r="P26">
-        <v>6.297869706666666</v>
+        <v>6.260503166666664</v>
       </c>
       <c r="Q26">
-        <v>16.29786970666667</v>
+        <v>16.26050316666667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1057284357304689</v>
+        <v>0.106372827512517</v>
       </c>
       <c r="T26">
-        <v>0.8249374751917258</v>
+        <v>0.8338077706238949</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.022626065399091</v>
+        <v>7.701721022783125</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08994462063438777</v>
+        <v>0.0899353101136191</v>
       </c>
       <c r="C27">
-        <v>72.35057898035839</v>
+        <v>71.44150123813353</v>
       </c>
       <c r="D27">
-        <v>87.1855789803584</v>
+        <v>87.19550123813353</v>
       </c>
       <c r="E27">
-        <v>-28.825</v>
+        <v>-27.906</v>
       </c>
       <c r="F27">
-        <v>22.975</v>
+        <v>23.894</v>
       </c>
       <c r="G27">
         <v>8.140000000000001</v>
@@ -3501,45 +3501,45 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M27">
-        <v>1.2291625</v>
+        <v>1.2974442</v>
       </c>
       <c r="N27">
-        <v>8.237504166666664</v>
+        <v>8.169222466666664</v>
       </c>
       <c r="O27">
-        <v>1.977000999999999</v>
+        <v>1.960613391999999</v>
       </c>
       <c r="P27">
-        <v>6.260503166666664</v>
+        <v>6.208609074666665</v>
       </c>
       <c r="Q27">
-        <v>16.26050316666667</v>
+        <v>16.20860907466666</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.106372827512517</v>
+        <v>0.1070346352886745</v>
       </c>
       <c r="T27">
-        <v>0.8338077706238949</v>
+        <v>0.8429178037704469</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.24</v>
       </c>
       <c r="W27">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.701721022783125</v>
+        <v>7.296395996580556</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0899353101136191</v>
+        <v>0.08977399959285046</v>
       </c>
       <c r="C28">
-        <v>71.44150123813353</v>
+        <v>70.69476971706968</v>
       </c>
       <c r="D28">
-        <v>87.19550123813353</v>
+        <v>87.36776971706968</v>
       </c>
       <c r="E28">
-        <v>-27.906</v>
+        <v>-26.987</v>
       </c>
       <c r="F28">
-        <v>23.894</v>
+        <v>24.813</v>
       </c>
       <c r="G28">
         <v>8.140000000000001</v>
@@ -3583,28 +3583,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M28">
-        <v>1.2974442</v>
+        <v>1.3473459</v>
       </c>
       <c r="N28">
-        <v>8.169222466666664</v>
+        <v>8.119320766666664</v>
       </c>
       <c r="O28">
-        <v>1.960613391999999</v>
+        <v>1.948636983999999</v>
       </c>
       <c r="P28">
-        <v>6.208609074666665</v>
+        <v>6.170683782666665</v>
       </c>
       <c r="Q28">
-        <v>16.20860907466666</v>
+        <v>16.17068378266666</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1070346352886745</v>
+        <v>0.1077145747847267</v>
       </c>
       <c r="T28">
-        <v>0.8429178037704469</v>
+        <v>0.8522774268662195</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.296395996580556</v>
+        <v>7.026159107818314</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08977399959285046</v>
+        <v>0.08961268907208179</v>
       </c>
       <c r="C29">
-        <v>70.69476971706968</v>
+        <v>69.94872023062796</v>
       </c>
       <c r="D29">
-        <v>87.36776971706968</v>
+        <v>87.54072023062795</v>
       </c>
       <c r="E29">
-        <v>-26.987</v>
+        <v>-26.068</v>
       </c>
       <c r="F29">
-        <v>24.813</v>
+        <v>25.732</v>
       </c>
       <c r="G29">
         <v>8.140000000000001</v>
@@ -3665,28 +3665,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M29">
-        <v>1.3473459</v>
+        <v>1.3972476</v>
       </c>
       <c r="N29">
-        <v>8.119320766666664</v>
+        <v>8.069419066666665</v>
       </c>
       <c r="O29">
-        <v>1.948636983999999</v>
+        <v>1.936660576</v>
       </c>
       <c r="P29">
-        <v>6.170683782666665</v>
+        <v>6.132758490666665</v>
       </c>
       <c r="Q29">
-        <v>16.17068378266666</v>
+        <v>16.13275849066667</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1077145747847267</v>
+        <v>0.1084134014890025</v>
       </c>
       <c r="T29">
-        <v>0.8522774268662195</v>
+        <v>0.8618970394924304</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.026159107818314</v>
+        <v>6.77522485396766</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08961268907208179</v>
+        <v>0.08945137855131316</v>
       </c>
       <c r="C30">
-        <v>69.94872023062796</v>
+        <v>69.20335683724568</v>
       </c>
       <c r="D30">
-        <v>87.54072023062795</v>
+        <v>87.71435683724569</v>
       </c>
       <c r="E30">
-        <v>-26.068</v>
+        <v>-25.149</v>
       </c>
       <c r="F30">
-        <v>25.732</v>
+        <v>26.651</v>
       </c>
       <c r="G30">
         <v>8.140000000000001</v>
@@ -3747,28 +3747,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M30">
-        <v>1.3972476</v>
+        <v>1.4471493</v>
       </c>
       <c r="N30">
-        <v>8.069419066666665</v>
+        <v>8.019517366666665</v>
       </c>
       <c r="O30">
-        <v>1.936660576</v>
+        <v>1.924684168</v>
       </c>
       <c r="P30">
-        <v>6.132758490666665</v>
+        <v>6.094833198666666</v>
       </c>
       <c r="Q30">
-        <v>16.13275849066667</v>
+        <v>16.09483319866667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1084134014890025</v>
+        <v>0.1091319134525537</v>
       </c>
       <c r="T30">
-        <v>0.8618970394924304</v>
+        <v>0.8717876271221965</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.77522485396766</v>
+        <v>6.541596410727396</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08945137855131316</v>
+        <v>0.0892900680305445</v>
       </c>
       <c r="C31">
-        <v>69.20335683724569</v>
+        <v>68.45868362762394</v>
       </c>
       <c r="D31">
-        <v>87.71435683724569</v>
+        <v>87.88868362762393</v>
       </c>
       <c r="E31">
-        <v>-25.149</v>
+        <v>-24.23</v>
       </c>
       <c r="F31">
-        <v>26.651</v>
+        <v>27.57</v>
       </c>
       <c r="G31">
         <v>8.140000000000001</v>
@@ -3829,28 +3829,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M31">
-        <v>1.4471493</v>
+        <v>1.497051</v>
       </c>
       <c r="N31">
-        <v>8.019517366666665</v>
+        <v>7.969615666666665</v>
       </c>
       <c r="O31">
-        <v>1.924684168</v>
+        <v>1.91270776</v>
       </c>
       <c r="P31">
-        <v>6.094833198666666</v>
+        <v>6.056907906666666</v>
       </c>
       <c r="Q31">
-        <v>16.09483319866667</v>
+        <v>16.05690790666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1091319134525537</v>
+        <v>0.1098709543293493</v>
       </c>
       <c r="T31">
-        <v>0.8717876271221965</v>
+        <v>0.8819608029699556</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.541596410727397</v>
+        <v>6.323543197036483</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0892900680305445</v>
+        <v>0.08912875750977585</v>
       </c>
       <c r="C32">
-        <v>68.45868362762394</v>
+        <v>67.71470472504835</v>
       </c>
       <c r="D32">
-        <v>87.88868362762393</v>
+        <v>88.06370472504835</v>
       </c>
       <c r="E32">
-        <v>-24.23</v>
+        <v>-23.311</v>
       </c>
       <c r="F32">
-        <v>27.57</v>
+        <v>28.489</v>
       </c>
       <c r="G32">
         <v>8.140000000000001</v>
@@ -3911,28 +3911,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M32">
-        <v>1.497051</v>
+        <v>1.5469527</v>
       </c>
       <c r="N32">
-        <v>7.969615666666665</v>
+        <v>7.919713966666665</v>
       </c>
       <c r="O32">
-        <v>1.91270776</v>
+        <v>1.900731352</v>
       </c>
       <c r="P32">
-        <v>6.056907906666666</v>
+        <v>6.018982614666665</v>
       </c>
       <c r="Q32">
-        <v>16.05690790666667</v>
+        <v>16.01898261466667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1098709543293493</v>
+        <v>0.1106314166808346</v>
       </c>
       <c r="T32">
-        <v>0.8819608029699556</v>
+        <v>0.8924288534799689</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.323543197036483</v>
+        <v>6.119557932615952</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08912875750977585</v>
+        <v>0.08921064698900719</v>
       </c>
       <c r="C33">
-        <v>67.71470472504835</v>
+        <v>66.70676802948294</v>
       </c>
       <c r="D33">
-        <v>88.06370472504835</v>
+        <v>87.97476802948295</v>
       </c>
       <c r="E33">
-        <v>-23.311</v>
+        <v>-22.392</v>
       </c>
       <c r="F33">
-        <v>28.489</v>
+        <v>29.408</v>
       </c>
       <c r="G33">
         <v>8.140000000000001</v>
@@ -3993,45 +3993,45 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M33">
-        <v>1.5469527</v>
+        <v>1.6262624</v>
       </c>
       <c r="N33">
-        <v>7.919713966666665</v>
+        <v>7.840404266666665</v>
       </c>
       <c r="O33">
-        <v>1.900731352</v>
+        <v>1.881697023999999</v>
       </c>
       <c r="P33">
-        <v>6.018982614666665</v>
+        <v>5.958707242666666</v>
       </c>
       <c r="Q33">
-        <v>16.01898261466667</v>
+        <v>15.95870724266667</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1106314166808346</v>
+        <v>0.1114142455720694</v>
       </c>
       <c r="T33">
-        <v>0.8924288534799689</v>
+        <v>0.9032047878285119</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.24</v>
       </c>
       <c r="W33">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.119557932615952</v>
+        <v>5.821118822317151</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08921064698900719</v>
+        <v>0.08905693646823855</v>
       </c>
       <c r="C34">
-        <v>66.70676802948294</v>
+        <v>65.95485466220373</v>
       </c>
       <c r="D34">
-        <v>87.97476802948295</v>
+        <v>88.14185466220373</v>
       </c>
       <c r="E34">
-        <v>-22.392</v>
+        <v>-21.473</v>
       </c>
       <c r="F34">
-        <v>29.408</v>
+        <v>30.327</v>
       </c>
       <c r="G34">
         <v>8.140000000000001</v>
@@ -4075,28 +4075,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M34">
-        <v>1.6262624</v>
+        <v>1.6770831</v>
       </c>
       <c r="N34">
-        <v>7.840404266666665</v>
+        <v>7.789583566666665</v>
       </c>
       <c r="O34">
-        <v>1.881697023999999</v>
+        <v>1.869500055999999</v>
       </c>
       <c r="P34">
-        <v>5.958707242666666</v>
+        <v>5.920083510666665</v>
       </c>
       <c r="Q34">
-        <v>15.95870724266667</v>
+        <v>15.92008351066666</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1114142455720694</v>
+        <v>0.1122204424899083</v>
       </c>
       <c r="T34">
-        <v>0.9032047878285119</v>
+        <v>0.9143023918591009</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.821118822317151</v>
+        <v>5.644721282246935</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08905693646823855</v>
+        <v>0.0889032259474699</v>
       </c>
       <c r="C35">
-        <v>65.95485466220373</v>
+        <v>65.20357718332039</v>
       </c>
       <c r="D35">
-        <v>88.14185466220373</v>
+        <v>88.3095771833204</v>
       </c>
       <c r="E35">
-        <v>-21.473</v>
+        <v>-20.554</v>
       </c>
       <c r="F35">
-        <v>30.327</v>
+        <v>31.24600000000001</v>
       </c>
       <c r="G35">
         <v>8.140000000000001</v>
@@ -4157,28 +4157,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M35">
-        <v>1.6770831</v>
+        <v>1.7279038</v>
       </c>
       <c r="N35">
-        <v>7.789583566666665</v>
+        <v>7.738762866666665</v>
       </c>
       <c r="O35">
-        <v>1.869500055999999</v>
+        <v>1.857303087999999</v>
       </c>
       <c r="P35">
-        <v>5.920083510666665</v>
+        <v>5.881459778666666</v>
       </c>
       <c r="Q35">
-        <v>15.92008351066666</v>
+        <v>15.88145977866667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1122204424899083</v>
+        <v>0.1130510696173787</v>
       </c>
       <c r="T35">
-        <v>0.9143023918591009</v>
+        <v>0.9257362869209201</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.644721282246935</v>
+        <v>5.4787000680632</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0889032259474699</v>
+        <v>0.08874951542670126</v>
       </c>
       <c r="C36">
-        <v>65.20357718332039</v>
+        <v>64.45293922979307</v>
       </c>
       <c r="D36">
-        <v>88.3095771833204</v>
+        <v>88.47793922979308</v>
       </c>
       <c r="E36">
-        <v>-20.554</v>
+        <v>-19.635</v>
       </c>
       <c r="F36">
-        <v>31.24600000000001</v>
+        <v>32.16500000000001</v>
       </c>
       <c r="G36">
         <v>8.140000000000001</v>
@@ -4239,28 +4239,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M36">
-        <v>1.7279038</v>
+        <v>1.7787245</v>
       </c>
       <c r="N36">
-        <v>7.738762866666665</v>
+        <v>7.687942166666664</v>
       </c>
       <c r="O36">
-        <v>1.857303087999999</v>
+        <v>1.845106119999999</v>
       </c>
       <c r="P36">
-        <v>5.881459778666666</v>
+        <v>5.842836046666664</v>
       </c>
       <c r="Q36">
-        <v>15.88145977866667</v>
+        <v>15.84283604666667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1130510696173787</v>
+        <v>0.1139072545026173</v>
       </c>
       <c r="T36">
-        <v>0.9257362869209201</v>
+        <v>0.9375219941384874</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.4787000680632</v>
+        <v>5.322165780404251</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08874951542670126</v>
+        <v>0.08859580490593262</v>
       </c>
       <c r="C37">
-        <v>64.45293922979307</v>
+        <v>63.70294446637038</v>
       </c>
       <c r="D37">
-        <v>88.47793922979308</v>
+        <v>88.64694446637039</v>
       </c>
       <c r="E37">
-        <v>-19.635</v>
+        <v>-18.716</v>
       </c>
       <c r="F37">
-        <v>32.16500000000001</v>
+        <v>33.084</v>
       </c>
       <c r="G37">
         <v>8.140000000000001</v>
@@ -4321,28 +4321,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M37">
-        <v>1.7787245</v>
+        <v>1.8295452</v>
       </c>
       <c r="N37">
-        <v>7.687942166666664</v>
+        <v>7.637121466666665</v>
       </c>
       <c r="O37">
-        <v>1.845106119999999</v>
+        <v>1.832909152</v>
       </c>
       <c r="P37">
-        <v>5.842836046666664</v>
+        <v>5.804212314666666</v>
       </c>
       <c r="Q37">
-        <v>15.84283604666667</v>
+        <v>15.80421231466667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1139072545026173</v>
+        <v>0.1147901951655197</v>
       </c>
       <c r="T37">
-        <v>0.9375219941384874</v>
+        <v>0.9496760047066038</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.322165780404251</v>
+        <v>5.174327842059689</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08859580490593261</v>
+        <v>0.08844209438516396</v>
       </c>
       <c r="C38">
-        <v>63.7029444663704</v>
+        <v>62.95359658585524</v>
       </c>
       <c r="D38">
-        <v>88.6469444663704</v>
+        <v>88.81659658585524</v>
       </c>
       <c r="E38">
-        <v>-18.716</v>
+        <v>-17.797</v>
       </c>
       <c r="F38">
-        <v>33.084</v>
+        <v>34.003</v>
       </c>
       <c r="G38">
         <v>8.140000000000001</v>
@@ -4403,28 +4403,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M38">
-        <v>1.8295452</v>
+        <v>1.8803659</v>
       </c>
       <c r="N38">
-        <v>7.637121466666665</v>
+        <v>7.586300766666665</v>
       </c>
       <c r="O38">
-        <v>1.832909152</v>
+        <v>1.820712184</v>
       </c>
       <c r="P38">
-        <v>5.804212314666666</v>
+        <v>5.765588582666665</v>
       </c>
       <c r="Q38">
-        <v>15.80421231466667</v>
+        <v>15.76558858266667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1147901951655197</v>
+        <v>0.1157011656907364</v>
       </c>
       <c r="T38">
-        <v>0.9496760047066036</v>
+        <v>0.962215856880057</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.174327842059689</v>
+        <v>5.034481143625644</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08844209438516396</v>
+        <v>0.0882883838643953</v>
       </c>
       <c r="C39">
-        <v>62.95359658585524</v>
+        <v>62.20489930937375</v>
       </c>
       <c r="D39">
-        <v>88.81659658585524</v>
+        <v>88.98689930937375</v>
       </c>
       <c r="E39">
-        <v>-17.797</v>
+        <v>-16.878</v>
       </c>
       <c r="F39">
-        <v>34.003</v>
+        <v>34.922</v>
       </c>
       <c r="G39">
         <v>8.140000000000001</v>
@@ -4485,28 +4485,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M39">
-        <v>1.8803659</v>
+        <v>1.9311866</v>
       </c>
       <c r="N39">
-        <v>7.586300766666665</v>
+        <v>7.535480066666665</v>
       </c>
       <c r="O39">
-        <v>1.820712184</v>
+        <v>1.808515216</v>
       </c>
       <c r="P39">
-        <v>5.765588582666665</v>
+        <v>5.726964850666665</v>
       </c>
       <c r="Q39">
-        <v>15.76558858266667</v>
+        <v>15.72696485066666</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1157011656907364</v>
+        <v>0.1166415223619279</v>
       </c>
       <c r="T39">
-        <v>0.962215856880057</v>
+        <v>0.9751602204139443</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.034481143625644</v>
+        <v>4.901994797740759</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0882883838643953</v>
+        <v>0.08813467334362665</v>
       </c>
       <c r="C40">
-        <v>62.20489930937375</v>
+        <v>61.45685638664752</v>
       </c>
       <c r="D40">
-        <v>88.98689930937375</v>
+        <v>89.15785638664752</v>
       </c>
       <c r="E40">
-        <v>-16.878</v>
+        <v>-15.959</v>
       </c>
       <c r="F40">
-        <v>34.922</v>
+        <v>35.841</v>
       </c>
       <c r="G40">
         <v>8.140000000000001</v>
@@ -4567,28 +4567,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M40">
-        <v>1.9311866</v>
+        <v>1.9820073</v>
       </c>
       <c r="N40">
-        <v>7.535480066666665</v>
+        <v>7.484659366666665</v>
       </c>
       <c r="O40">
-        <v>1.808515216</v>
+        <v>1.796318248</v>
       </c>
       <c r="P40">
-        <v>5.726964850666665</v>
+        <v>5.688341118666665</v>
       </c>
       <c r="Q40">
-        <v>15.72696485066666</v>
+        <v>15.68834111866667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1166415223619279</v>
+        <v>0.1176127103993879</v>
       </c>
       <c r="T40">
-        <v>0.9751602204139443</v>
+        <v>0.9885289893095984</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.901994797740759</v>
+        <v>4.776302623439714</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08813467334362665</v>
+        <v>0.08798096282285801</v>
       </c>
       <c r="C41">
-        <v>61.45685638664752</v>
+        <v>60.70947159626856</v>
       </c>
       <c r="D41">
-        <v>89.15785638664752</v>
+        <v>89.32947159626856</v>
       </c>
       <c r="E41">
-        <v>-15.959</v>
+        <v>-15.04</v>
       </c>
       <c r="F41">
-        <v>35.841</v>
+        <v>36.76000000000001</v>
       </c>
       <c r="G41">
         <v>8.140000000000001</v>
@@ -4649,28 +4649,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M41">
-        <v>1.9820073</v>
+        <v>2.032828</v>
       </c>
       <c r="N41">
-        <v>7.484659366666665</v>
+        <v>7.433838666666665</v>
       </c>
       <c r="O41">
-        <v>1.796318248</v>
+        <v>1.784121279999999</v>
       </c>
       <c r="P41">
-        <v>5.688341118666665</v>
+        <v>5.649717386666666</v>
       </c>
       <c r="Q41">
-        <v>15.68834111866667</v>
+        <v>15.64971738666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1176127103993879</v>
+        <v>0.11861627137143</v>
       </c>
       <c r="T41">
-        <v>0.9885289893095984</v>
+        <v>1.002343383835108</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.776302623439714</v>
+        <v>4.65689505785372</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08798096282285801</v>
+        <v>0.08782725230208936</v>
       </c>
       <c r="C42">
-        <v>60.70947159626856</v>
+        <v>59.96274874597798</v>
       </c>
       <c r="D42">
-        <v>89.32947159626856</v>
+        <v>89.50174874597798</v>
       </c>
       <c r="E42">
-        <v>-15.04</v>
+        <v>-14.121</v>
       </c>
       <c r="F42">
-        <v>36.76000000000001</v>
+        <v>37.679</v>
       </c>
       <c r="G42">
         <v>8.140000000000001</v>
@@ -4731,28 +4731,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M42">
-        <v>2.032828</v>
+        <v>2.0836487</v>
       </c>
       <c r="N42">
-        <v>7.433838666666665</v>
+        <v>7.383017966666665</v>
       </c>
       <c r="O42">
-        <v>1.784121279999999</v>
+        <v>1.771924311999999</v>
       </c>
       <c r="P42">
-        <v>5.649717386666666</v>
+        <v>5.611093654666665</v>
       </c>
       <c r="Q42">
-        <v>15.64971738666667</v>
+        <v>15.61109365466666</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.11861627137143</v>
+        <v>0.1196538513594735</v>
       </c>
       <c r="T42">
-        <v>1.002343383835108</v>
+        <v>1.016626062920804</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.65689505785372</v>
+        <v>4.543312251564606</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08782725230208936</v>
+        <v>0.08847154178132069</v>
       </c>
       <c r="C43">
-        <v>59.96274874597798</v>
+        <v>58.32604488010758</v>
       </c>
       <c r="D43">
-        <v>89.50174874597798</v>
+        <v>88.78404488010759</v>
       </c>
       <c r="E43">
-        <v>-14.121</v>
+        <v>-13.202</v>
       </c>
       <c r="F43">
-        <v>37.679</v>
+        <v>38.59800000000001</v>
       </c>
       <c r="G43">
         <v>8.140000000000001</v>
@@ -4813,45 +4813,45 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M43">
-        <v>2.0836487</v>
+        <v>2.2309644</v>
       </c>
       <c r="N43">
-        <v>7.383017966666665</v>
+        <v>7.235702266666665</v>
       </c>
       <c r="O43">
-        <v>1.771924311999999</v>
+        <v>1.736568543999999</v>
       </c>
       <c r="P43">
-        <v>5.611093654666665</v>
+        <v>5.499133722666665</v>
       </c>
       <c r="Q43">
-        <v>15.61109365466666</v>
+        <v>15.49913372266666</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1196538513594735</v>
+        <v>0.1207272099677943</v>
       </c>
       <c r="T43">
-        <v>1.016626062920804</v>
+        <v>1.031401248181869</v>
       </c>
       <c r="U43">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.24</v>
       </c>
       <c r="W43">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.543312251564606</v>
+        <v>4.243306915460714</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.0884715417813207</v>
+        <v>0.08833683126055206</v>
       </c>
       <c r="C44">
-        <v>58.32604488010756</v>
+        <v>57.55615184296104</v>
       </c>
       <c r="D44">
-        <v>88.78404488010756</v>
+        <v>88.93315184296104</v>
       </c>
       <c r="E44">
-        <v>-13.20200000000001</v>
+        <v>-12.283</v>
       </c>
       <c r="F44">
-        <v>38.598</v>
+        <v>39.517</v>
       </c>
       <c r="G44">
         <v>8.140000000000001</v>
@@ -4895,28 +4895,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M44">
-        <v>2.2309644</v>
+        <v>2.284082600000001</v>
       </c>
       <c r="N44">
-        <v>7.235702266666665</v>
+        <v>7.182584066666664</v>
       </c>
       <c r="O44">
-        <v>1.736568544</v>
+        <v>1.723820175999999</v>
       </c>
       <c r="P44">
-        <v>5.499133722666666</v>
+        <v>5.458763890666665</v>
       </c>
       <c r="Q44">
-        <v>15.49913372266667</v>
+        <v>15.45876389066667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1207272099677943</v>
+        <v>0.1218382302816703</v>
       </c>
       <c r="T44">
-        <v>1.031401248181868</v>
+        <v>1.046694860995953</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.243306915460716</v>
+        <v>4.144625359287209</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08833683126055206</v>
+        <v>0.08820212073978341</v>
       </c>
       <c r="C45">
-        <v>57.55615184296104</v>
+        <v>56.78676047901235</v>
       </c>
       <c r="D45">
-        <v>88.93315184296104</v>
+        <v>89.08276047901235</v>
       </c>
       <c r="E45">
-        <v>-12.283</v>
+        <v>-11.364</v>
       </c>
       <c r="F45">
-        <v>39.517</v>
+        <v>40.436</v>
       </c>
       <c r="G45">
         <v>8.140000000000001</v>
@@ -4977,28 +4977,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M45">
-        <v>2.284082600000001</v>
+        <v>2.3372008</v>
       </c>
       <c r="N45">
-        <v>7.182584066666664</v>
+        <v>7.129465866666665</v>
       </c>
       <c r="O45">
-        <v>1.723820175999999</v>
+        <v>1.711071808</v>
       </c>
       <c r="P45">
-        <v>5.458763890666665</v>
+        <v>5.418394058666665</v>
       </c>
       <c r="Q45">
-        <v>15.45876389066667</v>
+        <v>15.41839405866667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1218382302816703</v>
+        <v>0.1229889298924704</v>
       </c>
       <c r="T45">
-        <v>1.046694860995953</v>
+        <v>1.062534674267684</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.144625359287209</v>
+        <v>4.050429328394319</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08820212073978341</v>
+        <v>0.08926441021901477</v>
       </c>
       <c r="C46">
-        <v>56.78676047901235</v>
+        <v>54.70147568121257</v>
       </c>
       <c r="D46">
-        <v>89.08276047901235</v>
+        <v>87.91647568121257</v>
       </c>
       <c r="E46">
-        <v>-11.364</v>
+        <v>-10.445</v>
       </c>
       <c r="F46">
-        <v>40.436</v>
+        <v>41.355</v>
       </c>
       <c r="G46">
         <v>8.140000000000001</v>
@@ -5059,45 +5059,45 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M46">
-        <v>2.3372008</v>
+        <v>2.5350615</v>
       </c>
       <c r="N46">
-        <v>7.129465866666665</v>
+        <v>6.931605166666665</v>
       </c>
       <c r="O46">
-        <v>1.711071808</v>
+        <v>1.66358524</v>
       </c>
       <c r="P46">
-        <v>5.418394058666665</v>
+        <v>5.268019926666665</v>
       </c>
       <c r="Q46">
-        <v>15.41839405866667</v>
+        <v>15.26801992666666</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1229889298924704</v>
+        <v>0.1241814731254814</v>
       </c>
       <c r="T46">
-        <v>1.062534674267684</v>
+        <v>1.078950480749295</v>
       </c>
       <c r="U46">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V46">
         <v>0.24</v>
       </c>
       <c r="W46">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.050429328394319</v>
+        <v>3.734294677532148</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08926441021901477</v>
+        <v>0.08915629969824612</v>
       </c>
       <c r="C47">
-        <v>54.70147568121257</v>
+        <v>53.89977225840059</v>
       </c>
       <c r="D47">
-        <v>87.91647568121257</v>
+        <v>88.03377225840059</v>
       </c>
       <c r="E47">
-        <v>-10.445</v>
+        <v>-9.526000000000003</v>
       </c>
       <c r="F47">
-        <v>41.355</v>
+        <v>42.274</v>
       </c>
       <c r="G47">
         <v>8.140000000000001</v>
@@ -5141,28 +5141,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M47">
-        <v>2.5350615</v>
+        <v>2.5913962</v>
       </c>
       <c r="N47">
-        <v>6.931605166666665</v>
+        <v>6.875270466666665</v>
       </c>
       <c r="O47">
-        <v>1.66358524</v>
+        <v>1.650064911999999</v>
       </c>
       <c r="P47">
-        <v>5.268019926666665</v>
+        <v>5.225205554666665</v>
       </c>
       <c r="Q47">
-        <v>15.26801992666666</v>
+        <v>15.22520555466667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1241814731254814</v>
+        <v>0.1254181846263817</v>
       </c>
       <c r="T47">
-        <v>1.078950480749295</v>
+        <v>1.095974280063559</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.734294677532148</v>
+        <v>3.653114358455363</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08915629969824612</v>
+        <v>0.08904818917747746</v>
       </c>
       <c r="C48">
-        <v>53.89977225840059</v>
+        <v>53.09838224369017</v>
       </c>
       <c r="D48">
-        <v>88.03377225840059</v>
+        <v>88.15138224369018</v>
       </c>
       <c r="E48">
-        <v>-9.526000000000003</v>
+        <v>-8.606999999999999</v>
       </c>
       <c r="F48">
-        <v>42.274</v>
+        <v>43.193</v>
       </c>
       <c r="G48">
         <v>8.140000000000001</v>
@@ -5223,28 +5223,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M48">
-        <v>2.5913962</v>
+        <v>2.6477309</v>
       </c>
       <c r="N48">
-        <v>6.875270466666665</v>
+        <v>6.818935766666664</v>
       </c>
       <c r="O48">
-        <v>1.650064911999999</v>
+        <v>1.636544583999999</v>
       </c>
       <c r="P48">
-        <v>5.225205554666665</v>
+        <v>5.182391182666665</v>
       </c>
       <c r="Q48">
-        <v>15.22520555466667</v>
+        <v>15.18239118266666</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1254181846263817</v>
+        <v>0.1267015644858065</v>
       </c>
       <c r="T48">
-        <v>1.095974280063559</v>
+        <v>1.113640486899116</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.653114358455363</v>
+        <v>3.575388521041418</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08904818917747746</v>
+        <v>0.08894007865670883</v>
       </c>
       <c r="C49">
-        <v>53.09838224369017</v>
+        <v>52.2973068948678</v>
       </c>
       <c r="D49">
-        <v>88.15138224369018</v>
+        <v>88.26930689486781</v>
       </c>
       <c r="E49">
-        <v>-8.606999999999999</v>
+        <v>-7.687999999999995</v>
       </c>
       <c r="F49">
-        <v>43.193</v>
+        <v>44.11200000000001</v>
       </c>
       <c r="G49">
         <v>8.140000000000001</v>
@@ -5305,28 +5305,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M49">
-        <v>2.6477309</v>
+        <v>2.704065600000001</v>
       </c>
       <c r="N49">
-        <v>6.818935766666664</v>
+        <v>6.762601066666664</v>
       </c>
       <c r="O49">
-        <v>1.636544583999999</v>
+        <v>1.623024255999999</v>
       </c>
       <c r="P49">
-        <v>5.182391182666665</v>
+        <v>5.139576810666664</v>
       </c>
       <c r="Q49">
-        <v>15.18239118266666</v>
+        <v>15.13957681066666</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1267015644858065</v>
+        <v>0.1280343051090554</v>
       </c>
       <c r="T49">
-        <v>1.113640486899116</v>
+        <v>1.131986163228348</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.575388521041418</v>
+        <v>3.500901260186388</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08894007865670883</v>
+        <v>0.08987468813594016</v>
       </c>
       <c r="C50">
-        <v>52.29730689486781</v>
+        <v>50.36916157897715</v>
       </c>
       <c r="D50">
-        <v>88.26930689486781</v>
+        <v>87.26016157897715</v>
       </c>
       <c r="E50">
-        <v>-7.688000000000002</v>
+        <v>-6.769000000000005</v>
       </c>
       <c r="F50">
-        <v>44.112</v>
+        <v>45.031</v>
       </c>
       <c r="G50">
         <v>8.140000000000001</v>
@@ -5387,45 +5387,45 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M50">
-        <v>2.7040656</v>
+        <v>2.8864871</v>
       </c>
       <c r="N50">
-        <v>6.762601066666665</v>
+        <v>6.580179566666665</v>
       </c>
       <c r="O50">
-        <v>1.623024256</v>
+        <v>1.579243095999999</v>
       </c>
       <c r="P50">
-        <v>5.139576810666665</v>
+        <v>5.000936470666666</v>
       </c>
       <c r="Q50">
-        <v>15.13957681066666</v>
+        <v>15.00093647066667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1280343051090554</v>
+        <v>0.1294193100704709</v>
       </c>
       <c r="T50">
-        <v>1.131986163228348</v>
+        <v>1.151051277845001</v>
       </c>
       <c r="U50">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0.24</v>
       </c>
       <c r="W50">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.500901260186389</v>
+        <v>3.279649739874696</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08987468813594016</v>
+        <v>0.08978785761517151</v>
       </c>
       <c r="C51">
-        <v>50.36916157897715</v>
+        <v>49.54294358555985</v>
       </c>
       <c r="D51">
-        <v>87.26016157897715</v>
+        <v>87.35294358555986</v>
       </c>
       <c r="E51">
-        <v>-6.769000000000005</v>
+        <v>-5.850000000000001</v>
       </c>
       <c r="F51">
-        <v>45.031</v>
+        <v>45.95</v>
       </c>
       <c r="G51">
         <v>8.140000000000001</v>
@@ -5469,28 +5469,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M51">
-        <v>2.8864871</v>
+        <v>2.945395</v>
       </c>
       <c r="N51">
-        <v>6.580179566666665</v>
+        <v>6.521271666666665</v>
       </c>
       <c r="O51">
-        <v>1.579243095999999</v>
+        <v>1.565105199999999</v>
       </c>
       <c r="P51">
-        <v>5.000936470666666</v>
+        <v>4.956166466666665</v>
       </c>
       <c r="Q51">
-        <v>15.00093647066667</v>
+        <v>14.95616646666667</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1294193100704709</v>
+        <v>0.130859715230343</v>
       </c>
       <c r="T51">
-        <v>1.151051277845001</v>
+        <v>1.17087899704632</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.279649739874696</v>
+        <v>3.214056745077202</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08978785761517151</v>
+        <v>0.08970102709440288</v>
       </c>
       <c r="C52">
-        <v>49.54294358555985</v>
+        <v>48.71692310870865</v>
       </c>
       <c r="D52">
-        <v>87.35294358555986</v>
+        <v>87.44592310870866</v>
       </c>
       <c r="E52">
-        <v>-5.850000000000001</v>
+        <v>-4.930999999999997</v>
       </c>
       <c r="F52">
-        <v>45.95</v>
+        <v>46.86900000000001</v>
       </c>
       <c r="G52">
         <v>8.140000000000001</v>
@@ -5551,28 +5551,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M52">
-        <v>2.945395</v>
+        <v>3.004302900000001</v>
       </c>
       <c r="N52">
-        <v>6.521271666666665</v>
+        <v>6.462363766666664</v>
       </c>
       <c r="O52">
-        <v>1.565105199999999</v>
+        <v>1.550967303999999</v>
       </c>
       <c r="P52">
-        <v>4.956166466666665</v>
+        <v>4.911396462666665</v>
       </c>
       <c r="Q52">
-        <v>14.95616646666667</v>
+        <v>14.91139646266667</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.130859715230343</v>
+        <v>0.1323589124375569</v>
       </c>
       <c r="T52">
-        <v>1.17087899704632</v>
+        <v>1.191516010908918</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.214056745077202</v>
+        <v>3.151036024585491</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08970102709440288</v>
+        <v>0.08961419657363422</v>
       </c>
       <c r="C53">
-        <v>48.71692310870865</v>
+        <v>47.8911007798127</v>
       </c>
       <c r="D53">
-        <v>87.44592310870866</v>
+        <v>87.5391007798127</v>
       </c>
       <c r="E53">
-        <v>-4.930999999999997</v>
+        <v>-4.012</v>
       </c>
       <c r="F53">
-        <v>46.86900000000001</v>
+        <v>47.788</v>
       </c>
       <c r="G53">
         <v>8.140000000000001</v>
@@ -5633,28 +5633,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M53">
-        <v>3.004302900000001</v>
+        <v>3.0632108</v>
       </c>
       <c r="N53">
-        <v>6.462363766666664</v>
+        <v>6.403455866666665</v>
       </c>
       <c r="O53">
-        <v>1.550967303999999</v>
+        <v>1.536829408</v>
       </c>
       <c r="P53">
-        <v>4.911396462666665</v>
+        <v>4.866626458666666</v>
       </c>
       <c r="Q53">
-        <v>14.91139646266667</v>
+        <v>14.86662645866667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1323589124375569</v>
+        <v>0.1339205761950713</v>
       </c>
       <c r="T53">
-        <v>1.191516010908918</v>
+        <v>1.213012900349124</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.151036024585491</v>
+        <v>3.090439177958848</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08961419657363422</v>
+        <v>0.08952736605286557</v>
       </c>
       <c r="C54">
-        <v>47.8911007798127</v>
+        <v>47.06547723295499</v>
       </c>
       <c r="D54">
-        <v>87.5391007798127</v>
+        <v>87.632477232955</v>
       </c>
       <c r="E54">
-        <v>-4.012</v>
+        <v>-3.092999999999996</v>
       </c>
       <c r="F54">
-        <v>47.788</v>
+        <v>48.70700000000001</v>
       </c>
       <c r="G54">
         <v>8.140000000000001</v>
@@ -5715,28 +5715,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M54">
-        <v>3.0632108</v>
+        <v>3.122118700000001</v>
       </c>
       <c r="N54">
-        <v>6.403455866666665</v>
+        <v>6.344547966666664</v>
       </c>
       <c r="O54">
-        <v>1.536829408</v>
+        <v>1.522691511999999</v>
       </c>
       <c r="P54">
-        <v>4.866626458666666</v>
+        <v>4.821856454666666</v>
       </c>
       <c r="Q54">
-        <v>14.86662645866667</v>
+        <v>14.82185645466667</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1339205761950713</v>
+        <v>0.1355486937295012</v>
       </c>
       <c r="T54">
-        <v>1.213012900349124</v>
+        <v>1.235424551042104</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.090439177958848</v>
+        <v>3.032129004789812</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08952736605286557</v>
+        <v>0.09264165553209691</v>
       </c>
       <c r="C55">
-        <v>47.06547723295499</v>
+        <v>42.91737583657228</v>
       </c>
       <c r="D55">
-        <v>87.632477232955</v>
+        <v>84.40337583657228</v>
       </c>
       <c r="E55">
-        <v>-3.092999999999996</v>
+        <v>-2.173999999999999</v>
       </c>
       <c r="F55">
-        <v>48.70700000000001</v>
+        <v>49.626</v>
       </c>
       <c r="G55">
         <v>8.140000000000001</v>
@@ -5797,45 +5797,45 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M55">
-        <v>3.122118700000001</v>
+        <v>3.5681094</v>
       </c>
       <c r="N55">
-        <v>6.344547966666664</v>
+        <v>5.898557266666664</v>
       </c>
       <c r="O55">
-        <v>1.522691511999999</v>
+        <v>1.415653743999999</v>
       </c>
       <c r="P55">
-        <v>4.821856454666666</v>
+        <v>4.482903522666665</v>
       </c>
       <c r="Q55">
-        <v>14.82185645466667</v>
+        <v>14.48290352266666</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1355486937295012</v>
+        <v>0.1372475989828194</v>
       </c>
       <c r="T55">
-        <v>1.235424551042104</v>
+        <v>1.258810621330432</v>
       </c>
       <c r="U55">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V55">
         <v>0.24</v>
       </c>
       <c r="W55">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.032129004789812</v>
+        <v>2.653132403021798</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09264165553209691</v>
+        <v>0.09261410501132826</v>
       </c>
       <c r="C56">
-        <v>42.91737583657228</v>
+        <v>42.02589839725933</v>
       </c>
       <c r="D56">
-        <v>84.40337583657228</v>
+        <v>84.43089839725934</v>
       </c>
       <c r="E56">
-        <v>-2.173999999999999</v>
+        <v>-1.254999999999995</v>
       </c>
       <c r="F56">
-        <v>49.626</v>
+        <v>50.54500000000001</v>
       </c>
       <c r="G56">
         <v>8.140000000000001</v>
@@ -5879,28 +5879,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M56">
-        <v>3.5681094</v>
+        <v>3.634185500000001</v>
       </c>
       <c r="N56">
-        <v>5.898557266666664</v>
+        <v>5.832481166666664</v>
       </c>
       <c r="O56">
-        <v>1.415653743999999</v>
+        <v>1.399795479999999</v>
       </c>
       <c r="P56">
-        <v>4.482903522666665</v>
+        <v>4.432685686666664</v>
       </c>
       <c r="Q56">
-        <v>14.48290352266666</v>
+        <v>14.43268568666666</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1372475989828194</v>
+        <v>0.139022011136285</v>
       </c>
       <c r="T56">
-        <v>1.258810621330432</v>
+        <v>1.283236072520463</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.653132403021798</v>
+        <v>2.604893632057764</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09261410501132826</v>
+        <v>0.09258655449055961</v>
       </c>
       <c r="C57">
-        <v>42.02589839725933</v>
+        <v>41.13443891311531</v>
       </c>
       <c r="D57">
-        <v>84.43089839725934</v>
+        <v>84.45843891311532</v>
       </c>
       <c r="E57">
-        <v>-1.254999999999995</v>
+        <v>-0.3359999999999985</v>
       </c>
       <c r="F57">
-        <v>50.54500000000001</v>
+        <v>51.46400000000001</v>
       </c>
       <c r="G57">
         <v>8.140000000000001</v>
@@ -5961,28 +5961,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M57">
-        <v>3.634185500000001</v>
+        <v>3.700261600000001</v>
       </c>
       <c r="N57">
-        <v>5.832481166666664</v>
+        <v>5.766405066666664</v>
       </c>
       <c r="O57">
-        <v>1.399795479999999</v>
+        <v>1.383937215999999</v>
       </c>
       <c r="P57">
-        <v>4.432685686666664</v>
+        <v>4.382467850666664</v>
       </c>
       <c r="Q57">
-        <v>14.43268568666666</v>
+        <v>14.38246785066666</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.139022011136285</v>
+        <v>0.1408770783876355</v>
       </c>
       <c r="T57">
-        <v>1.283236072520463</v>
+        <v>1.308771771491858</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.604893632057764</v>
+        <v>2.558377674342447</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09258655449055961</v>
+        <v>0.09255900396979097</v>
       </c>
       <c r="C58">
-        <v>41.13443891311531</v>
+        <v>40.24299740171622</v>
       </c>
       <c r="D58">
-        <v>84.45843891311532</v>
+        <v>84.48599740171623</v>
       </c>
       <c r="E58">
-        <v>-0.3359999999999985</v>
+        <v>0.5830000000000055</v>
       </c>
       <c r="F58">
-        <v>51.46400000000001</v>
+        <v>52.38300000000001</v>
       </c>
       <c r="G58">
         <v>8.140000000000001</v>
@@ -6043,28 +6043,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M58">
-        <v>3.700261600000001</v>
+        <v>3.766337700000001</v>
       </c>
       <c r="N58">
-        <v>5.766405066666664</v>
+        <v>5.700328966666664</v>
       </c>
       <c r="O58">
-        <v>1.383937215999999</v>
+        <v>1.368078951999999</v>
       </c>
       <c r="P58">
-        <v>4.382467850666664</v>
+        <v>4.332250014666664</v>
       </c>
       <c r="Q58">
-        <v>14.38246785066666</v>
+        <v>14.33225001466666</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1408770783876355</v>
+        <v>0.1428184278367232</v>
       </c>
       <c r="T58">
-        <v>1.308771771491858</v>
+        <v>1.335495177392156</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.558377674342447</v>
+        <v>2.513493855494334</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09255900396979097</v>
+        <v>0.09425057344902232</v>
       </c>
       <c r="C59">
-        <v>40.24299740171622</v>
+        <v>37.66463070672981</v>
       </c>
       <c r="D59">
-        <v>84.48599740171623</v>
+        <v>82.82663070672982</v>
       </c>
       <c r="E59">
-        <v>0.5830000000000055</v>
+        <v>1.502000000000002</v>
       </c>
       <c r="F59">
-        <v>52.38300000000001</v>
+        <v>53.30200000000001</v>
       </c>
       <c r="G59">
         <v>8.140000000000001</v>
@@ -6125,45 +6125,45 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M59">
-        <v>3.766337700000001</v>
+        <v>4.040291600000001</v>
       </c>
       <c r="N59">
-        <v>5.700328966666664</v>
+        <v>5.426375066666664</v>
       </c>
       <c r="O59">
-        <v>1.368078951999999</v>
+        <v>1.302330015999999</v>
       </c>
       <c r="P59">
-        <v>4.332250014666664</v>
+        <v>4.124045050666665</v>
       </c>
       <c r="Q59">
-        <v>14.33225001466666</v>
+        <v>14.12404505066667</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1428184278367232</v>
+        <v>0.1448522224976722</v>
       </c>
       <c r="T59">
-        <v>1.335495177392156</v>
+        <v>1.363491126430564</v>
       </c>
       <c r="U59">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V59">
         <v>0.24</v>
       </c>
       <c r="W59">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.513493855494334</v>
+        <v>2.343065205161594</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09425057344902232</v>
+        <v>0.09425266292825368</v>
       </c>
       <c r="C60">
-        <v>37.66463070672982</v>
+        <v>36.74362131176028</v>
       </c>
       <c r="D60">
-        <v>82.82663070672982</v>
+        <v>82.82462131176028</v>
       </c>
       <c r="E60">
-        <v>1.501999999999995</v>
+        <v>2.420999999999999</v>
       </c>
       <c r="F60">
-        <v>53.302</v>
+        <v>54.221</v>
       </c>
       <c r="G60">
         <v>8.140000000000001</v>
@@ -6207,28 +6207,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M60">
-        <v>4.040291600000001</v>
+        <v>4.109951800000001</v>
       </c>
       <c r="N60">
-        <v>5.426375066666664</v>
+        <v>5.356714866666664</v>
       </c>
       <c r="O60">
-        <v>1.302330015999999</v>
+        <v>1.285611567999999</v>
       </c>
       <c r="P60">
-        <v>4.124045050666665</v>
+        <v>4.071103298666665</v>
       </c>
       <c r="Q60">
-        <v>14.12404505066667</v>
+        <v>14.07110329866666</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1448522224976722</v>
+        <v>0.1469852266542772</v>
       </c>
       <c r="T60">
-        <v>1.363491126430564</v>
+        <v>1.392852731519625</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.343065205161594</v>
+        <v>2.303352235582583</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09425266292825368</v>
+        <v>0.09425475240748502</v>
       </c>
       <c r="C61">
-        <v>36.74362131176028</v>
+        <v>35.8226120142853</v>
       </c>
       <c r="D61">
-        <v>82.82462131176028</v>
+        <v>82.8226120142853</v>
       </c>
       <c r="E61">
-        <v>2.420999999999999</v>
+        <v>3.339999999999996</v>
       </c>
       <c r="F61">
-        <v>54.221</v>
+        <v>55.14</v>
       </c>
       <c r="G61">
         <v>8.140000000000001</v>
@@ -6289,28 +6289,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M61">
-        <v>4.109951800000001</v>
+        <v>4.179612000000001</v>
       </c>
       <c r="N61">
-        <v>5.356714866666664</v>
+        <v>5.287054666666664</v>
       </c>
       <c r="O61">
-        <v>1.285611567999999</v>
+        <v>1.268893119999999</v>
       </c>
       <c r="P61">
-        <v>4.071103298666665</v>
+        <v>4.018161546666665</v>
       </c>
       <c r="Q61">
-        <v>14.07110329866666</v>
+        <v>14.01816154666666</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1469852266542772</v>
+        <v>0.1492248810187125</v>
       </c>
       <c r="T61">
-        <v>1.392852731519625</v>
+        <v>1.423682416863139</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.303352235582583</v>
+        <v>2.264963031656207</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09425475240748502</v>
+        <v>0.09425684188671637</v>
       </c>
       <c r="C62">
-        <v>35.8226120142853</v>
+        <v>34.90160281429765</v>
       </c>
       <c r="D62">
-        <v>82.8226120142853</v>
+        <v>82.82060281429766</v>
       </c>
       <c r="E62">
-        <v>3.339999999999996</v>
+        <v>4.259</v>
       </c>
       <c r="F62">
-        <v>55.14</v>
+        <v>56.059</v>
       </c>
       <c r="G62">
         <v>8.140000000000001</v>
@@ -6371,28 +6371,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M62">
-        <v>4.179612000000001</v>
+        <v>4.249272200000001</v>
       </c>
       <c r="N62">
-        <v>5.287054666666664</v>
+        <v>5.217394466666664</v>
       </c>
       <c r="O62">
-        <v>1.268893119999999</v>
+        <v>1.252174671999999</v>
       </c>
       <c r="P62">
-        <v>4.018161546666665</v>
+        <v>3.965219794666665</v>
       </c>
       <c r="Q62">
-        <v>14.01816154666666</v>
+        <v>13.96521979466666</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1492248810187125</v>
+        <v>0.1515793894531189</v>
       </c>
       <c r="T62">
-        <v>1.423682416863139</v>
+        <v>1.45609311171145</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.264963031656207</v>
+        <v>2.227832490153646</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09425684188671637</v>
+        <v>0.09425893136594773</v>
       </c>
       <c r="C63">
-        <v>34.90160281429765</v>
+        <v>33.98059371179033</v>
       </c>
       <c r="D63">
-        <v>82.82060281429766</v>
+        <v>82.81859371179033</v>
       </c>
       <c r="E63">
-        <v>4.259</v>
+        <v>5.177999999999997</v>
       </c>
       <c r="F63">
-        <v>56.059</v>
+        <v>56.978</v>
       </c>
       <c r="G63">
         <v>8.140000000000001</v>
@@ -6453,28 +6453,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M63">
-        <v>4.249272200000001</v>
+        <v>4.3189324</v>
       </c>
       <c r="N63">
-        <v>5.217394466666664</v>
+        <v>5.147734266666665</v>
       </c>
       <c r="O63">
-        <v>1.252174671999999</v>
+        <v>1.235456224</v>
       </c>
       <c r="P63">
-        <v>3.965219794666665</v>
+        <v>3.912278042666665</v>
       </c>
       <c r="Q63">
-        <v>13.96521979466666</v>
+        <v>13.91227804266667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1515793894531189</v>
+        <v>0.154057819384073</v>
       </c>
       <c r="T63">
-        <v>1.45609311171145</v>
+        <v>1.490209632604408</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.227832490153646</v>
+        <v>2.191899708054394</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09425893136594773</v>
+        <v>0.09426102084517907</v>
       </c>
       <c r="C64">
-        <v>33.98059371179033</v>
+        <v>33.05958470675623</v>
       </c>
       <c r="D64">
-        <v>82.81859371179033</v>
+        <v>82.81658470675623</v>
       </c>
       <c r="E64">
-        <v>5.177999999999997</v>
+        <v>6.097000000000001</v>
       </c>
       <c r="F64">
-        <v>56.978</v>
+        <v>57.89700000000001</v>
       </c>
       <c r="G64">
         <v>8.140000000000001</v>
@@ -6535,28 +6535,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M64">
-        <v>4.3189324</v>
+        <v>4.388592600000001</v>
       </c>
       <c r="N64">
-        <v>5.147734266666665</v>
+        <v>5.078074066666664</v>
       </c>
       <c r="O64">
-        <v>1.235456224</v>
+        <v>1.218737775999999</v>
       </c>
       <c r="P64">
-        <v>3.912278042666665</v>
+        <v>3.859336290666665</v>
       </c>
       <c r="Q64">
-        <v>13.91227804266667</v>
+        <v>13.85933629066666</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.154057819384073</v>
+        <v>0.1566702185004839</v>
       </c>
       <c r="T64">
-        <v>1.490209632604408</v>
+        <v>1.52617028976185</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.191899708054394</v>
+        <v>2.157107649196388</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09426102084517907</v>
+        <v>0.09426311032441041</v>
       </c>
       <c r="C65">
-        <v>33.05958470675623</v>
+        <v>32.13857579918825</v>
       </c>
       <c r="D65">
-        <v>82.81658470675623</v>
+        <v>82.81457579918825</v>
       </c>
       <c r="E65">
-        <v>6.097000000000001</v>
+        <v>7.015999999999998</v>
       </c>
       <c r="F65">
-        <v>57.89700000000001</v>
+        <v>58.816</v>
       </c>
       <c r="G65">
         <v>8.140000000000001</v>
@@ -6617,28 +6617,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M65">
-        <v>4.388592600000001</v>
+        <v>4.4582528</v>
       </c>
       <c r="N65">
-        <v>5.078074066666664</v>
+        <v>5.008413866666665</v>
       </c>
       <c r="O65">
-        <v>1.218737775999999</v>
+        <v>1.202019328</v>
       </c>
       <c r="P65">
-        <v>3.859336290666665</v>
+        <v>3.806394538666665</v>
       </c>
       <c r="Q65">
-        <v>13.85933629066666</v>
+        <v>13.80639453866667</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1566702185004839</v>
+        <v>0.15942775090114</v>
       </c>
       <c r="T65">
-        <v>1.52617028976185</v>
+        <v>1.564128761205817</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.157107649196388</v>
+        <v>2.123402842177694</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09426311032441041</v>
+        <v>0.09426519980364179</v>
       </c>
       <c r="C66">
-        <v>32.13857579918825</v>
+        <v>31.21756698907925</v>
       </c>
       <c r="D66">
-        <v>82.81457579918825</v>
+        <v>82.81256698907926</v>
       </c>
       <c r="E66">
-        <v>7.015999999999998</v>
+        <v>7.935000000000002</v>
       </c>
       <c r="F66">
-        <v>58.816</v>
+        <v>59.73500000000001</v>
       </c>
       <c r="G66">
         <v>8.140000000000001</v>
@@ -6699,28 +6699,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M66">
-        <v>4.4582528</v>
+        <v>4.527913000000001</v>
       </c>
       <c r="N66">
-        <v>5.008413866666665</v>
+        <v>4.938753666666664</v>
       </c>
       <c r="O66">
-        <v>1.202019328</v>
+        <v>1.185300879999999</v>
       </c>
       <c r="P66">
-        <v>3.806394538666665</v>
+        <v>3.753452786666665</v>
       </c>
       <c r="Q66">
-        <v>13.80639453866667</v>
+        <v>13.75345278666667</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.15942775090114</v>
+        <v>0.1623428565818336</v>
       </c>
       <c r="T66">
-        <v>1.564128761205817</v>
+        <v>1.604256288160868</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.123402842177694</v>
+        <v>2.090735106144191</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09426519980364179</v>
+        <v>0.09426728928287312</v>
       </c>
       <c r="C67">
-        <v>31.21756698907925</v>
+        <v>30.29655827642224</v>
       </c>
       <c r="D67">
-        <v>82.81256698907926</v>
+        <v>82.81055827642224</v>
       </c>
       <c r="E67">
-        <v>7.935000000000002</v>
+        <v>8.853999999999999</v>
       </c>
       <c r="F67">
-        <v>59.73500000000001</v>
+        <v>60.654</v>
       </c>
       <c r="G67">
         <v>8.140000000000001</v>
@@ -6781,28 +6781,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M67">
-        <v>4.527913000000001</v>
+        <v>4.5975732</v>
       </c>
       <c r="N67">
-        <v>4.938753666666664</v>
+        <v>4.869093466666665</v>
       </c>
       <c r="O67">
-        <v>1.185300879999999</v>
+        <v>1.168582432</v>
       </c>
       <c r="P67">
-        <v>3.753452786666665</v>
+        <v>3.700511034666665</v>
       </c>
       <c r="Q67">
-        <v>13.75345278666667</v>
+        <v>13.70051103466666</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1623428565818336</v>
+        <v>0.1654294390672739</v>
       </c>
       <c r="T67">
-        <v>1.604256288160868</v>
+        <v>1.64674425787798</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.090735106144191</v>
+        <v>2.059057301505643</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09426728928287312</v>
+        <v>0.09426937876210448</v>
       </c>
       <c r="C68">
-        <v>30.29655827642224</v>
+        <v>29.37554966121003</v>
       </c>
       <c r="D68">
-        <v>82.81055827642224</v>
+        <v>82.80854966121004</v>
       </c>
       <c r="E68">
-        <v>8.853999999999999</v>
+        <v>9.773000000000003</v>
       </c>
       <c r="F68">
-        <v>60.654</v>
+        <v>61.57300000000001</v>
       </c>
       <c r="G68">
         <v>8.140000000000001</v>
@@ -6863,28 +6863,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M68">
-        <v>4.5975732</v>
+        <v>4.667233400000001</v>
       </c>
       <c r="N68">
-        <v>4.869093466666665</v>
+        <v>4.799433266666664</v>
       </c>
       <c r="O68">
-        <v>1.168582432</v>
+        <v>1.151863983999999</v>
       </c>
       <c r="P68">
-        <v>3.700511034666665</v>
+        <v>3.647569282666665</v>
       </c>
       <c r="Q68">
-        <v>13.70051103466666</v>
+        <v>13.64756928266667</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1654294390672739</v>
+        <v>0.1687030871578923</v>
       </c>
       <c r="T68">
-        <v>1.64674425787798</v>
+        <v>1.691807256062797</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.059057301505643</v>
+        <v>2.028325102975708</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09426937876210448</v>
+        <v>0.1016100282413358</v>
       </c>
       <c r="C69">
-        <v>29.37554966121003</v>
+        <v>21.9542418082842</v>
       </c>
       <c r="D69">
-        <v>82.80854966121004</v>
+        <v>76.30624180828421</v>
       </c>
       <c r="E69">
-        <v>9.773000000000003</v>
+        <v>10.69200000000001</v>
       </c>
       <c r="F69">
-        <v>61.57300000000001</v>
+        <v>62.49200000000001</v>
       </c>
       <c r="G69">
         <v>8.140000000000001</v>
@@ -6945,45 +6945,45 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M69">
-        <v>4.667233400000001</v>
+        <v>5.624280000000001</v>
       </c>
       <c r="N69">
-        <v>4.799433266666664</v>
+        <v>3.842386666666664</v>
       </c>
       <c r="O69">
-        <v>1.151863983999999</v>
+        <v>0.9221727999999995</v>
       </c>
       <c r="P69">
-        <v>3.647569282666665</v>
+        <v>2.920213866666665</v>
       </c>
       <c r="Q69">
-        <v>13.64756928266667</v>
+        <v>12.92021386666666</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1687030871578923</v>
+        <v>0.1721813382541744</v>
       </c>
       <c r="T69">
-        <v>1.691807256062797</v>
+        <v>1.739686691634164</v>
       </c>
       <c r="U69">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V69">
         <v>0.24</v>
       </c>
       <c r="W69">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.028325102975708</v>
+        <v>1.683178409799417</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1016100282413358</v>
+        <v>0.1017200377205672</v>
       </c>
       <c r="C70">
-        <v>21.9542418082842</v>
+        <v>20.94555320194618</v>
       </c>
       <c r="D70">
-        <v>76.30624180828421</v>
+        <v>76.21655320194618</v>
       </c>
       <c r="E70">
-        <v>10.69200000000001</v>
+        <v>11.611</v>
       </c>
       <c r="F70">
-        <v>62.49200000000001</v>
+        <v>63.41100000000001</v>
       </c>
       <c r="G70">
         <v>8.140000000000001</v>
@@ -7027,28 +7027,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M70">
-        <v>5.624280000000001</v>
+        <v>5.70699</v>
       </c>
       <c r="N70">
-        <v>3.842386666666664</v>
+        <v>3.759676666666665</v>
       </c>
       <c r="O70">
-        <v>0.9221727999999995</v>
+        <v>0.9023223999999995</v>
       </c>
       <c r="P70">
-        <v>2.920213866666665</v>
+        <v>2.857354266666665</v>
       </c>
       <c r="Q70">
-        <v>12.92021386666666</v>
+        <v>12.85735426666666</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1721813382541744</v>
+        <v>0.1758839926469909</v>
       </c>
       <c r="T70">
-        <v>1.739686691634164</v>
+        <v>1.790655123048845</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.683178409799417</v>
+        <v>1.658784519802324</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1017200377205672</v>
+        <v>0.1018300471997985</v>
       </c>
       <c r="C71">
-        <v>20.94555320194618</v>
+        <v>19.93707518394876</v>
       </c>
       <c r="D71">
-        <v>76.21655320194618</v>
+        <v>76.12707518394878</v>
       </c>
       <c r="E71">
-        <v>11.611</v>
+        <v>12.53000000000001</v>
       </c>
       <c r="F71">
-        <v>63.41100000000001</v>
+        <v>64.33000000000001</v>
       </c>
       <c r="G71">
         <v>8.140000000000001</v>
@@ -7109,28 +7109,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M71">
-        <v>5.70699</v>
+        <v>5.789700000000001</v>
       </c>
       <c r="N71">
-        <v>3.759676666666665</v>
+        <v>3.676966666666664</v>
       </c>
       <c r="O71">
-        <v>0.9023223999999995</v>
+        <v>0.8824719999999994</v>
       </c>
       <c r="P71">
-        <v>2.857354266666665</v>
+        <v>2.794494666666665</v>
       </c>
       <c r="Q71">
-        <v>12.85735426666666</v>
+        <v>12.79449466666667</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1758839926469909</v>
+        <v>0.1798334906659951</v>
       </c>
       <c r="T71">
-        <v>1.790655123048845</v>
+        <v>1.845021449891172</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.658784519802324</v>
+        <v>1.635087598090862</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1018300471997985</v>
+        <v>0.1019400566790299</v>
       </c>
       <c r="C72">
-        <v>19.93707518394876</v>
+        <v>18.9288070134713</v>
       </c>
       <c r="D72">
-        <v>76.12707518394878</v>
+        <v>76.03780701347131</v>
       </c>
       <c r="E72">
-        <v>12.53000000000001</v>
+        <v>13.44900000000001</v>
       </c>
       <c r="F72">
-        <v>64.33000000000001</v>
+        <v>65.24900000000001</v>
       </c>
       <c r="G72">
         <v>8.140000000000001</v>
@@ -7191,28 +7191,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M72">
-        <v>5.789700000000001</v>
+        <v>5.87241</v>
       </c>
       <c r="N72">
-        <v>3.676966666666664</v>
+        <v>3.594256666666665</v>
       </c>
       <c r="O72">
-        <v>0.8824719999999994</v>
+        <v>0.8626215999999994</v>
       </c>
       <c r="P72">
-        <v>2.794494666666665</v>
+        <v>2.731635066666665</v>
       </c>
       <c r="Q72">
-        <v>12.79449466666667</v>
+        <v>12.73163506666667</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1798334906659951</v>
+        <v>0.1840553678587238</v>
       </c>
       <c r="T72">
-        <v>1.845021449891172</v>
+        <v>1.903137178584694</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.635087598090862</v>
+        <v>1.61205819530085</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1019400566790299</v>
+        <v>0.1020500661582612</v>
       </c>
       <c r="C73">
-        <v>18.92880701347131</v>
+        <v>17.92074795316391</v>
       </c>
       <c r="D73">
-        <v>76.03780701347131</v>
+        <v>75.94874795316392</v>
       </c>
       <c r="E73">
-        <v>13.44899999999999</v>
+        <v>14.368</v>
       </c>
       <c r="F73">
-        <v>65.249</v>
+        <v>66.16800000000001</v>
       </c>
       <c r="G73">
         <v>8.140000000000001</v>
@@ -7273,28 +7273,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M73">
-        <v>5.872409999999999</v>
+        <v>5.95512</v>
       </c>
       <c r="N73">
-        <v>3.594256666666666</v>
+        <v>3.511546666666665</v>
       </c>
       <c r="O73">
-        <v>0.8626215999999997</v>
+        <v>0.8427711999999996</v>
       </c>
       <c r="P73">
-        <v>2.731635066666666</v>
+        <v>2.668775466666665</v>
       </c>
       <c r="Q73">
-        <v>12.73163506666667</v>
+        <v>12.66877546666667</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1840553678587237</v>
+        <v>0.1885788077080758</v>
       </c>
       <c r="T73">
-        <v>1.903137178584693</v>
+        <v>1.965404030756324</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.61205819530085</v>
+        <v>1.589668498143894</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1020500661582612</v>
+        <v>0.1021600756374926</v>
       </c>
       <c r="C74">
-        <v>17.92074795316391</v>
+        <v>16.91289726912713</v>
       </c>
       <c r="D74">
-        <v>75.94874795316392</v>
+        <v>75.85989726912713</v>
       </c>
       <c r="E74">
-        <v>14.368</v>
+        <v>15.287</v>
       </c>
       <c r="F74">
-        <v>66.16800000000001</v>
+        <v>67.087</v>
       </c>
       <c r="G74">
         <v>8.140000000000001</v>
@@ -7355,28 +7355,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M74">
-        <v>5.95512</v>
+        <v>6.03783</v>
       </c>
       <c r="N74">
-        <v>3.511546666666665</v>
+        <v>3.428836666666665</v>
       </c>
       <c r="O74">
-        <v>0.8427711999999996</v>
+        <v>0.8229207999999995</v>
       </c>
       <c r="P74">
-        <v>2.668775466666665</v>
+        <v>2.605915866666665</v>
       </c>
       <c r="Q74">
-        <v>12.66877546666667</v>
+        <v>12.60591586666667</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1885788077080758</v>
+        <v>0.1934373171758984</v>
       </c>
       <c r="T74">
-        <v>1.965404030756324</v>
+        <v>2.032283242348075</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.589668498143894</v>
+        <v>1.567892217347402</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1021600756374926</v>
+        <v>0.1022700851167239</v>
       </c>
       <c r="C75">
-        <v>16.91289726912713</v>
+        <v>15.90525423089179</v>
       </c>
       <c r="D75">
-        <v>75.85989726912713</v>
+        <v>75.77125423089178</v>
       </c>
       <c r="E75">
-        <v>15.287</v>
+        <v>16.206</v>
       </c>
       <c r="F75">
-        <v>67.087</v>
+        <v>68.006</v>
       </c>
       <c r="G75">
         <v>8.140000000000001</v>
@@ -7437,28 +7437,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M75">
-        <v>6.03783</v>
+        <v>6.12054</v>
       </c>
       <c r="N75">
-        <v>3.428836666666665</v>
+        <v>3.346126666666665</v>
       </c>
       <c r="O75">
-        <v>0.8229207999999995</v>
+        <v>0.8030703999999995</v>
       </c>
       <c r="P75">
-        <v>2.605915866666665</v>
+        <v>2.543056266666666</v>
       </c>
       <c r="Q75">
-        <v>12.60591586666667</v>
+        <v>12.54305626666667</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1934373171758984</v>
+        <v>0.1986695581412458</v>
       </c>
       <c r="T75">
-        <v>2.032283242348075</v>
+        <v>2.104307008677653</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.567892217347402</v>
+        <v>1.546704484680545</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1022700851167239</v>
+        <v>0.1023800945959553</v>
       </c>
       <c r="C76">
-        <v>15.90525423089179</v>
+        <v>14.89781811139891</v>
       </c>
       <c r="D76">
-        <v>75.77125423089178</v>
+        <v>75.68281811139892</v>
       </c>
       <c r="E76">
-        <v>16.206</v>
+        <v>17.12500000000001</v>
       </c>
       <c r="F76">
-        <v>68.006</v>
+        <v>68.92500000000001</v>
       </c>
       <c r="G76">
         <v>8.140000000000001</v>
@@ -7519,28 +7519,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M76">
-        <v>6.12054</v>
+        <v>6.203250000000001</v>
       </c>
       <c r="N76">
-        <v>3.346126666666665</v>
+        <v>3.263416666666664</v>
       </c>
       <c r="O76">
-        <v>0.8030703999999995</v>
+        <v>0.7832199999999995</v>
       </c>
       <c r="P76">
-        <v>2.543056266666666</v>
+        <v>2.480196666666665</v>
       </c>
       <c r="Q76">
-        <v>12.54305626666667</v>
+        <v>12.48019666666666</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1986695581412458</v>
+        <v>0.2043203783838211</v>
       </c>
       <c r="T76">
-        <v>2.104307008677653</v>
+        <v>2.182092676313597</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.546704484680545</v>
+        <v>1.526081758218138</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1023800945959553</v>
+        <v>0.1024901040751866</v>
       </c>
       <c r="C77">
-        <v>14.89781811139891</v>
+        <v>13.89058818698001</v>
       </c>
       <c r="D77">
-        <v>75.68281811139892</v>
+        <v>75.59458818698002</v>
       </c>
       <c r="E77">
-        <v>17.12500000000001</v>
+        <v>18.044</v>
       </c>
       <c r="F77">
-        <v>68.92500000000001</v>
+        <v>69.84400000000001</v>
       </c>
       <c r="G77">
         <v>8.140000000000001</v>
@@ -7601,28 +7601,28 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M77">
-        <v>6.203250000000001</v>
+        <v>6.28596</v>
       </c>
       <c r="N77">
-        <v>3.263416666666664</v>
+        <v>3.180706666666665</v>
       </c>
       <c r="O77">
-        <v>0.7832199999999995</v>
+        <v>0.7633695999999995</v>
       </c>
       <c r="P77">
-        <v>2.480196666666665</v>
+        <v>2.417337066666665</v>
       </c>
       <c r="Q77">
-        <v>12.48019666666666</v>
+        <v>12.41733706666666</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2043203783838211</v>
+        <v>0.2104421003132776</v>
       </c>
       <c r="T77">
-        <v>2.182092676313597</v>
+        <v>2.266360482919204</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.526081758218138</v>
+        <v>1.506001735083689</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1024901040751866</v>
+        <v>0.1390377285803408</v>
       </c>
       <c r="C78">
-        <v>13.89058818698001</v>
+        <v>-8.132565069363068</v>
       </c>
       <c r="D78">
-        <v>75.59458818698002</v>
+        <v>54.49043493063694</v>
       </c>
       <c r="E78">
-        <v>18.044</v>
+        <v>18.963</v>
       </c>
       <c r="F78">
-        <v>69.84400000000001</v>
+        <v>70.76300000000001</v>
       </c>
       <c r="G78">
         <v>8.140000000000001</v>
@@ -7683,45 +7683,45 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M78">
-        <v>6.28596</v>
+        <v>10.3880084</v>
       </c>
       <c r="N78">
-        <v>3.180706666666665</v>
+        <v>-0.9213417333333371</v>
       </c>
       <c r="O78">
-        <v>0.7633695999999995</v>
+        <v>-0.2211220160000009</v>
       </c>
       <c r="P78">
-        <v>2.417337066666665</v>
+        <v>-0.7002197173333362</v>
       </c>
       <c r="Q78">
-        <v>12.41733706666666</v>
+        <v>9.299780282666664</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2104421003132776</v>
+        <v>0.2205402307107592</v>
       </c>
       <c r="T78">
-        <v>2.266360482919204</v>
+        <v>2.405365048827136</v>
       </c>
       <c r="U78">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.24</v>
+        <v>0.2187137237971428</v>
       </c>
       <c r="W78">
-        <v>0.0684</v>
+        <v>0.1146928253465794</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.506001735083689</v>
+        <v>0.9113071824880949</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1390377285803408</v>
+        <v>0.1400477285803408</v>
       </c>
       <c r="C79">
-        <v>-8.132565069363068</v>
+        <v>-9.468743619413686</v>
       </c>
       <c r="D79">
-        <v>54.49043493063694</v>
+        <v>54.07325638058632</v>
       </c>
       <c r="E79">
-        <v>18.963</v>
+        <v>19.882</v>
       </c>
       <c r="F79">
-        <v>70.76300000000001</v>
+        <v>71.682</v>
       </c>
       <c r="G79">
         <v>8.140000000000001</v>
@@ -7765,37 +7765,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M79">
-        <v>10.3880084</v>
+        <v>10.5229176</v>
       </c>
       <c r="N79">
-        <v>-0.9213417333333371</v>
+        <v>-1.056250933333336</v>
       </c>
       <c r="O79">
-        <v>-0.2211220160000009</v>
+        <v>-0.2535002240000007</v>
       </c>
       <c r="P79">
-        <v>-0.7002197173333362</v>
+        <v>-0.8027507093333356</v>
       </c>
       <c r="Q79">
-        <v>9.299780282666664</v>
+        <v>9.197249290666665</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2205402307107592</v>
+        <v>0.2284829684703392</v>
       </c>
       <c r="T79">
-        <v>2.405365048827136</v>
+        <v>2.514699823773825</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2187137237971428</v>
+        <v>0.2159097016971794</v>
       </c>
       <c r="W79">
-        <v>0.1146928253465794</v>
+        <v>0.1151044557908541</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9113071824880949</v>
+        <v>0.8996237570715809</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1400477285803408</v>
+        <v>0.1410577285803408</v>
       </c>
       <c r="C80">
-        <v>-9.468743619413686</v>
+        <v>-10.79858286853356</v>
       </c>
       <c r="D80">
-        <v>54.07325638058632</v>
+        <v>53.66241713146646</v>
       </c>
       <c r="E80">
-        <v>19.882</v>
+        <v>20.80100000000001</v>
       </c>
       <c r="F80">
-        <v>71.682</v>
+        <v>72.60100000000001</v>
       </c>
       <c r="G80">
         <v>8.140000000000001</v>
@@ -7847,37 +7847,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M80">
-        <v>10.5229176</v>
+        <v>10.6578268</v>
       </c>
       <c r="N80">
-        <v>-1.056250933333336</v>
+        <v>-1.191160133333337</v>
       </c>
       <c r="O80">
-        <v>-0.2535002240000007</v>
+        <v>-0.2858784320000009</v>
       </c>
       <c r="P80">
-        <v>-0.8027507093333356</v>
+        <v>-0.9052817013333363</v>
       </c>
       <c r="Q80">
-        <v>9.197249290666665</v>
+        <v>9.094718298666663</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2284829684703392</v>
+        <v>0.2371821574451173</v>
       </c>
       <c r="T80">
-        <v>2.514699823773825</v>
+        <v>2.634447434429721</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.2159097016971794</v>
+        <v>0.2131766674984809</v>
       </c>
       <c r="W80">
-        <v>0.1151044557908541</v>
+        <v>0.115505665211223</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8996237570715809</v>
+        <v>0.8882361145770039</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1410577285803408</v>
+        <v>0.1420677285803408</v>
       </c>
       <c r="C81">
-        <v>-10.79858286853356</v>
+        <v>-12.12222622189092</v>
       </c>
       <c r="D81">
-        <v>53.66241713146646</v>
+        <v>53.25777377810909</v>
       </c>
       <c r="E81">
-        <v>20.80100000000001</v>
+        <v>21.72000000000001</v>
       </c>
       <c r="F81">
-        <v>72.60100000000001</v>
+        <v>73.52000000000001</v>
       </c>
       <c r="G81">
         <v>8.140000000000001</v>
@@ -7929,37 +7929,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M81">
-        <v>10.6578268</v>
+        <v>10.792736</v>
       </c>
       <c r="N81">
-        <v>-1.191160133333337</v>
+        <v>-1.326069333333338</v>
       </c>
       <c r="O81">
-        <v>-0.2858784320000009</v>
+        <v>-0.3182566400000011</v>
       </c>
       <c r="P81">
-        <v>-0.9052817013333363</v>
+        <v>-1.007812693333337</v>
       </c>
       <c r="Q81">
-        <v>9.094718298666663</v>
+        <v>8.992187306666663</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2371821574451173</v>
+        <v>0.2467512653173731</v>
       </c>
       <c r="T81">
-        <v>2.634447434429721</v>
+        <v>2.766169806151207</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.2131766674984809</v>
+        <v>0.2105119591547499</v>
       </c>
       <c r="W81">
-        <v>0.115505665211223</v>
+        <v>0.1158968443960827</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8882361145770039</v>
+        <v>0.8771331631447913</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1420677285803408</v>
+        <v>0.1430777285803408</v>
       </c>
       <c r="C82">
-        <v>-12.12222622189092</v>
+        <v>-13.43981279161891</v>
       </c>
       <c r="D82">
-        <v>53.25777377810909</v>
+        <v>52.85918720838109</v>
       </c>
       <c r="E82">
-        <v>21.72000000000001</v>
+        <v>22.639</v>
       </c>
       <c r="F82">
-        <v>73.52000000000001</v>
+        <v>74.43900000000001</v>
       </c>
       <c r="G82">
         <v>8.140000000000001</v>
@@ -8011,37 +8011,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M82">
-        <v>10.792736</v>
+        <v>10.9276452</v>
       </c>
       <c r="N82">
-        <v>-1.326069333333338</v>
+        <v>-1.460978533333337</v>
       </c>
       <c r="O82">
-        <v>-0.3182566400000011</v>
+        <v>-0.3506348480000009</v>
       </c>
       <c r="P82">
-        <v>-1.007812693333337</v>
+        <v>-1.110343685333336</v>
       </c>
       <c r="Q82">
-        <v>8.992187306666663</v>
+        <v>8.889656314666663</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2467512653173731</v>
+        <v>0.2573276477024979</v>
       </c>
       <c r="T82">
-        <v>2.766169806151207</v>
+        <v>2.911757690685481</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.2105119591547499</v>
+        <v>0.2079130460787653</v>
       </c>
       <c r="W82">
-        <v>0.1158968443960827</v>
+        <v>0.1162783648356372</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8771331631447913</v>
+        <v>0.8663043586615223</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1430777285803408</v>
+        <v>0.1440877285803408</v>
       </c>
       <c r="C83">
-        <v>-13.43981279161891</v>
+        <v>-14.75147755626965</v>
       </c>
       <c r="D83">
-        <v>52.85918720838109</v>
+        <v>52.46652244373036</v>
       </c>
       <c r="E83">
-        <v>22.639</v>
+        <v>23.558</v>
       </c>
       <c r="F83">
-        <v>74.43900000000001</v>
+        <v>75.358</v>
       </c>
       <c r="G83">
         <v>8.140000000000001</v>
@@ -8093,37 +8093,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M83">
-        <v>10.9276452</v>
+        <v>11.0625544</v>
       </c>
       <c r="N83">
-        <v>-1.460978533333337</v>
+        <v>-1.595887733333337</v>
       </c>
       <c r="O83">
-        <v>-0.3506348480000009</v>
+        <v>-0.3830130560000007</v>
       </c>
       <c r="P83">
-        <v>-1.110343685333336</v>
+        <v>-1.212874677333336</v>
       </c>
       <c r="Q83">
-        <v>8.889656314666663</v>
+        <v>8.787125322666665</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2573276477024979</v>
+        <v>0.2690791836859701</v>
       </c>
       <c r="T83">
-        <v>2.911757690685481</v>
+        <v>3.073522006834675</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.2079130460787653</v>
+        <v>0.2053775211265853</v>
       </c>
       <c r="W83">
-        <v>0.1162783648356372</v>
+        <v>0.1166505798986173</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8663043586615223</v>
+        <v>0.8557396713607721</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1440877285803408</v>
+        <v>0.1450977285803408</v>
       </c>
       <c r="C84">
-        <v>-14.75147755626965</v>
+        <v>-16.0573515132138</v>
       </c>
       <c r="D84">
-        <v>52.46652244373036</v>
+        <v>52.07964848678622</v>
       </c>
       <c r="E84">
-        <v>23.558</v>
+        <v>24.47700000000001</v>
       </c>
       <c r="F84">
-        <v>75.358</v>
+        <v>76.27700000000002</v>
       </c>
       <c r="G84">
         <v>8.140000000000001</v>
@@ -8175,37 +8175,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M84">
-        <v>11.0625544</v>
+        <v>11.1974636</v>
       </c>
       <c r="N84">
-        <v>-1.595887733333337</v>
+        <v>-1.730796933333338</v>
       </c>
       <c r="O84">
-        <v>-0.3830130560000007</v>
+        <v>-0.415391264000001</v>
       </c>
       <c r="P84">
-        <v>-1.212874677333336</v>
+        <v>-1.315405669333336</v>
       </c>
       <c r="Q84">
-        <v>8.787125322666665</v>
+        <v>8.684594330666663</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2690791836859701</v>
+        <v>0.2822132533145566</v>
       </c>
       <c r="T84">
-        <v>3.073522006834675</v>
+        <v>3.254317419001421</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2053775211265853</v>
+        <v>0.2029030931612048</v>
       </c>
       <c r="W84">
-        <v>0.1166505798986173</v>
+        <v>0.1170138259239351</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8557396713607721</v>
+        <v>0.8454295548383531</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1450977285803408</v>
+        <v>0.1461077285803408</v>
       </c>
       <c r="C85">
-        <v>-16.0573515132138</v>
+        <v>-17.35756182434691</v>
       </c>
       <c r="D85">
-        <v>52.07964848678622</v>
+        <v>51.6984381756531</v>
       </c>
       <c r="E85">
-        <v>24.47700000000001</v>
+        <v>25.39600000000001</v>
       </c>
       <c r="F85">
-        <v>76.27700000000002</v>
+        <v>77.19600000000001</v>
       </c>
       <c r="G85">
         <v>8.140000000000001</v>
@@ -8257,37 +8257,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M85">
-        <v>11.1974636</v>
+        <v>11.3323728</v>
       </c>
       <c r="N85">
-        <v>-1.730796933333338</v>
+        <v>-1.865706133333338</v>
       </c>
       <c r="O85">
-        <v>-0.415391264000001</v>
+        <v>-0.4477694720000012</v>
       </c>
       <c r="P85">
-        <v>-1.315405669333336</v>
+        <v>-1.417936661333337</v>
       </c>
       <c r="Q85">
-        <v>8.684594330666663</v>
+        <v>8.582063338666662</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2822132533145566</v>
+        <v>0.2969890816467164</v>
       </c>
       <c r="T85">
-        <v>3.254317419001421</v>
+        <v>3.45771225768901</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2029030931612048</v>
+        <v>0.2004875801473809</v>
       </c>
       <c r="W85">
-        <v>0.1170138259239351</v>
+        <v>0.1173684232343645</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8454295548383531</v>
+        <v>0.8353649172807536</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1461077285803408</v>
+        <v>0.1471177285803408</v>
       </c>
       <c r="C86">
-        <v>-17.3575618243469</v>
+        <v>-18.65223195544316</v>
       </c>
       <c r="D86">
-        <v>51.6984381756531</v>
+        <v>51.32276804455685</v>
       </c>
       <c r="E86">
-        <v>25.39599999999999</v>
+        <v>26.315</v>
       </c>
       <c r="F86">
-        <v>77.196</v>
+        <v>78.11500000000001</v>
       </c>
       <c r="G86">
         <v>8.140000000000001</v>
@@ -8339,37 +8339,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M86">
-        <v>11.3323728</v>
+        <v>11.467282</v>
       </c>
       <c r="N86">
-        <v>-1.865706133333335</v>
+        <v>-2.000615333333338</v>
       </c>
       <c r="O86">
-        <v>-0.4477694720000003</v>
+        <v>-0.480147680000001</v>
       </c>
       <c r="P86">
-        <v>-1.417936661333335</v>
+        <v>-1.520467653333337</v>
       </c>
       <c r="Q86">
-        <v>8.582063338666666</v>
+        <v>8.479532346666664</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2969890816467163</v>
+        <v>0.313735020423164</v>
       </c>
       <c r="T86">
-        <v>3.457712257689008</v>
+        <v>3.688226408201609</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2004875801473809</v>
+        <v>0.1981289027338823</v>
       </c>
       <c r="W86">
-        <v>0.1173684232343645</v>
+        <v>0.1177146770786661</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8353649172807539</v>
+        <v>0.8255370947245095</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1471177285803408</v>
+        <v>0.1481277285803408</v>
       </c>
       <c r="C87">
-        <v>-18.65223195544316</v>
+        <v>-19.9414818094771</v>
       </c>
       <c r="D87">
-        <v>51.32276804455685</v>
+        <v>50.9525181905229</v>
       </c>
       <c r="E87">
-        <v>26.315</v>
+        <v>27.234</v>
       </c>
       <c r="F87">
-        <v>78.11500000000001</v>
+        <v>79.03400000000001</v>
       </c>
       <c r="G87">
         <v>8.140000000000001</v>
@@ -8421,37 +8421,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M87">
-        <v>11.467282</v>
+        <v>11.6021912</v>
       </c>
       <c r="N87">
-        <v>-2.000615333333338</v>
+        <v>-2.135524533333337</v>
       </c>
       <c r="O87">
-        <v>-0.480147680000001</v>
+        <v>-0.5125258880000008</v>
       </c>
       <c r="P87">
-        <v>-1.520467653333337</v>
+        <v>-1.622998645333336</v>
       </c>
       <c r="Q87">
-        <v>8.479532346666664</v>
+        <v>8.377001354666664</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.313735020423164</v>
+        <v>0.3328732361676758</v>
       </c>
       <c r="T87">
-        <v>3.688226408201609</v>
+        <v>3.951671151644581</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1981289027338823</v>
+        <v>0.1958250782834883</v>
       </c>
       <c r="W87">
-        <v>0.1177146770786661</v>
+        <v>0.1180528785079839</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8255370947245095</v>
+        <v>0.8159378261812014</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1481277285803408</v>
+        <v>0.1491377285803408</v>
       </c>
       <c r="C88">
-        <v>-19.9414818094771</v>
+        <v>-21.2254278542159</v>
       </c>
       <c r="D88">
-        <v>50.9525181905229</v>
+        <v>50.5875721457841</v>
       </c>
       <c r="E88">
-        <v>27.234</v>
+        <v>28.153</v>
       </c>
       <c r="F88">
-        <v>79.03400000000001</v>
+        <v>79.953</v>
       </c>
       <c r="G88">
         <v>8.140000000000001</v>
@@ -8503,37 +8503,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M88">
-        <v>11.6021912</v>
+        <v>11.7371004</v>
       </c>
       <c r="N88">
-        <v>-2.135524533333337</v>
+        <v>-2.270433733333336</v>
       </c>
       <c r="O88">
-        <v>-0.5125258880000008</v>
+        <v>-0.5449040960000006</v>
       </c>
       <c r="P88">
-        <v>-1.622998645333336</v>
+        <v>-1.725529637333335</v>
       </c>
       <c r="Q88">
-        <v>8.377001354666664</v>
+        <v>8.274470362666666</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3328732361676758</v>
+        <v>0.3549557927959585</v>
       </c>
       <c r="T88">
-        <v>3.951671151644581</v>
+        <v>4.255645855617241</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1958250782834883</v>
+        <v>0.1935742153147126</v>
       </c>
       <c r="W88">
-        <v>0.1180528785079839</v>
+        <v>0.1183833051918002</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8159378261812014</v>
+        <v>0.8065592304779692</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1491377285803408</v>
+        <v>0.1998565385995987</v>
       </c>
       <c r="C89">
-        <v>-21.2254278542159</v>
+        <v>-35.52637464480269</v>
       </c>
       <c r="D89">
-        <v>50.5875721457841</v>
+        <v>37.20562535519731</v>
       </c>
       <c r="E89">
-        <v>28.153</v>
+        <v>29.072</v>
       </c>
       <c r="F89">
-        <v>79.953</v>
+        <v>80.872</v>
       </c>
       <c r="G89">
         <v>8.140000000000001</v>
@@ -8585,45 +8585,45 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M89">
-        <v>11.7371004</v>
+        <v>16.2390976</v>
       </c>
       <c r="N89">
-        <v>-2.270433733333336</v>
+        <v>-6.772430933333336</v>
       </c>
       <c r="O89">
-        <v>-0.5449040960000006</v>
+        <v>-1.625383424</v>
       </c>
       <c r="P89">
-        <v>-1.725529637333335</v>
+        <v>-5.147047509333335</v>
       </c>
       <c r="Q89">
-        <v>8.274470362666666</v>
+        <v>4.852952490666665</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3549557927959585</v>
+        <v>0.398958859022771</v>
       </c>
       <c r="T89">
-        <v>4.255645855617241</v>
+        <v>4.861364625202701</v>
       </c>
       <c r="U89">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1935742153147126</v>
+        <v>0.1399092521003137</v>
       </c>
       <c r="W89">
-        <v>0.1183833051918002</v>
+        <v>0.172706222178257</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.8065592304779692</v>
+        <v>0.5829552170846405</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1998565385995987</v>
+        <v>0.2014065385995987</v>
       </c>
       <c r="C90">
-        <v>-35.52637464480269</v>
+        <v>-36.7437410328231</v>
       </c>
       <c r="D90">
-        <v>37.20562535519731</v>
+        <v>36.90725896717691</v>
       </c>
       <c r="E90">
-        <v>29.072</v>
+        <v>29.99100000000001</v>
       </c>
       <c r="F90">
-        <v>80.872</v>
+        <v>81.79100000000001</v>
       </c>
       <c r="G90">
         <v>8.140000000000001</v>
@@ -8667,37 +8667,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M90">
-        <v>16.2390976</v>
+        <v>16.4236328</v>
       </c>
       <c r="N90">
-        <v>-6.772430933333336</v>
+        <v>-6.956966133333339</v>
       </c>
       <c r="O90">
-        <v>-1.625383424</v>
+        <v>-1.669671872000001</v>
       </c>
       <c r="P90">
-        <v>-5.147047509333335</v>
+        <v>-5.287294261333337</v>
       </c>
       <c r="Q90">
-        <v>4.852952490666665</v>
+        <v>4.712705738666663</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.398958859022771</v>
+        <v>0.4310642098430228</v>
       </c>
       <c r="T90">
-        <v>4.861364625202701</v>
+        <v>5.303306863857491</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1399092521003137</v>
+        <v>0.1383372380317708</v>
       </c>
       <c r="W90">
-        <v>0.172706222178257</v>
+        <v>0.1730218826032204</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5829552170846405</v>
+        <v>0.5764051584657118</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2014065385995987</v>
+        <v>0.2029565385995987</v>
       </c>
       <c r="C91">
-        <v>-36.7437410328231</v>
+        <v>-37.95636005943675</v>
       </c>
       <c r="D91">
-        <v>36.90725896717691</v>
+        <v>36.61363994056326</v>
       </c>
       <c r="E91">
-        <v>29.99100000000001</v>
+        <v>30.91</v>
       </c>
       <c r="F91">
-        <v>81.79100000000001</v>
+        <v>82.71000000000001</v>
       </c>
       <c r="G91">
         <v>8.140000000000001</v>
@@ -8749,37 +8749,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M91">
-        <v>16.4236328</v>
+        <v>16.608168</v>
       </c>
       <c r="N91">
-        <v>-6.956966133333339</v>
+        <v>-7.141501333333338</v>
       </c>
       <c r="O91">
-        <v>-1.669671872000001</v>
+        <v>-1.713960320000001</v>
       </c>
       <c r="P91">
-        <v>-5.287294261333337</v>
+        <v>-5.427541013333337</v>
       </c>
       <c r="Q91">
-        <v>4.712705738666663</v>
+        <v>4.572458986666663</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4310642098430228</v>
+        <v>0.4695906308273252</v>
       </c>
       <c r="T91">
-        <v>5.303306863857491</v>
+        <v>5.833637550243242</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1383372380317708</v>
+        <v>0.1368001576091956</v>
       </c>
       <c r="W91">
-        <v>0.1730218826032204</v>
+        <v>0.1733305283520735</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5764051584657118</v>
+        <v>0.5700006567049818</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2029565385995987</v>
+        <v>0.2045065385995987</v>
       </c>
       <c r="C92">
-        <v>-37.95636005943675</v>
+        <v>-39.16434413454179</v>
       </c>
       <c r="D92">
-        <v>36.61363994056326</v>
+        <v>36.32465586545821</v>
       </c>
       <c r="E92">
-        <v>30.91</v>
+        <v>31.829</v>
       </c>
       <c r="F92">
-        <v>82.71000000000001</v>
+        <v>83.629</v>
       </c>
       <c r="G92">
         <v>8.140000000000001</v>
@@ -8831,37 +8831,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M92">
-        <v>16.608168</v>
+        <v>16.7927032</v>
       </c>
       <c r="N92">
-        <v>-7.141501333333338</v>
+        <v>-7.326036533333337</v>
       </c>
       <c r="O92">
-        <v>-1.713960320000001</v>
+        <v>-1.758248768000001</v>
       </c>
       <c r="P92">
-        <v>-5.427541013333337</v>
+        <v>-5.567787765333336</v>
       </c>
       <c r="Q92">
-        <v>4.572458986666663</v>
+        <v>4.432212234666664</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4695906308273252</v>
+        <v>0.5166784786970281</v>
       </c>
       <c r="T92">
-        <v>5.833637550243242</v>
+        <v>6.481819500270269</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1368001576091956</v>
+        <v>0.1352968591739298</v>
       </c>
       <c r="W92">
-        <v>0.1733305283520735</v>
+        <v>0.1736323906778749</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5700006567049818</v>
+        <v>0.5637369132247072</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2045065385995987</v>
+        <v>0.2060565385995987</v>
       </c>
       <c r="C93">
-        <v>-39.16434413454179</v>
+        <v>-40.36780214691324</v>
       </c>
       <c r="D93">
-        <v>36.32465586545821</v>
+        <v>36.04019785308676</v>
       </c>
       <c r="E93">
-        <v>31.829</v>
+        <v>32.748</v>
       </c>
       <c r="F93">
-        <v>83.629</v>
+        <v>84.548</v>
       </c>
       <c r="G93">
         <v>8.140000000000001</v>
@@ -8913,37 +8913,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M93">
-        <v>16.7927032</v>
+        <v>16.9772384</v>
       </c>
       <c r="N93">
-        <v>-7.326036533333337</v>
+        <v>-7.510571733333336</v>
       </c>
       <c r="O93">
-        <v>-1.758248768000001</v>
+        <v>-1.802537216000001</v>
       </c>
       <c r="P93">
-        <v>-5.567787765333336</v>
+        <v>-5.708034517333335</v>
       </c>
       <c r="Q93">
-        <v>4.432212234666664</v>
+        <v>4.291965482666665</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5166784786970281</v>
+        <v>0.5755382885341566</v>
       </c>
       <c r="T93">
-        <v>6.481819500270269</v>
+        <v>7.292046937804054</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1352968591739298</v>
+        <v>0.1338262411394305</v>
       </c>
       <c r="W93">
-        <v>0.1736323906778749</v>
+        <v>0.1739276907792024</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5637369132247072</v>
+        <v>0.5576093380809605</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2060565385995987</v>
+        <v>0.2076065385995987</v>
       </c>
       <c r="C94">
-        <v>-40.36780214691324</v>
+        <v>-41.56683960100119</v>
       </c>
       <c r="D94">
-        <v>36.04019785308676</v>
+        <v>35.76016039899882</v>
       </c>
       <c r="E94">
-        <v>32.748</v>
+        <v>33.66700000000001</v>
       </c>
       <c r="F94">
-        <v>84.548</v>
+        <v>85.46700000000001</v>
       </c>
       <c r="G94">
         <v>8.140000000000001</v>
@@ -8995,37 +8995,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M94">
-        <v>16.9772384</v>
+        <v>17.1617736</v>
       </c>
       <c r="N94">
-        <v>-7.510571733333336</v>
+        <v>-7.695106933333339</v>
       </c>
       <c r="O94">
-        <v>-1.802537216000001</v>
+        <v>-1.846825664000001</v>
       </c>
       <c r="P94">
-        <v>-5.708034517333335</v>
+        <v>-5.848281269333338</v>
       </c>
       <c r="Q94">
-        <v>4.291965482666665</v>
+        <v>4.151718730666662</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5755382885341566</v>
+        <v>0.6512151868961791</v>
       </c>
       <c r="T94">
-        <v>7.292046937804054</v>
+        <v>8.33376792891892</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1338262411394305</v>
+        <v>0.1323872492992216</v>
       </c>
       <c r="W94">
-        <v>0.1739276907792024</v>
+        <v>0.1742166403407163</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5576093380809605</v>
+        <v>0.5516135387467564</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2076065385995987</v>
+        <v>0.2091565385995987</v>
       </c>
       <c r="C95">
-        <v>-41.56683960100119</v>
+        <v>-42.76155874740039</v>
       </c>
       <c r="D95">
-        <v>35.76016039899882</v>
+        <v>35.48444125259962</v>
       </c>
       <c r="E95">
-        <v>33.66700000000001</v>
+        <v>34.58600000000001</v>
       </c>
       <c r="F95">
-        <v>85.46700000000001</v>
+        <v>86.38600000000001</v>
       </c>
       <c r="G95">
         <v>8.140000000000001</v>
@@ -9077,37 +9077,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M95">
-        <v>17.1617736</v>
+        <v>17.3463088</v>
       </c>
       <c r="N95">
-        <v>-7.695106933333339</v>
+        <v>-7.879642133333338</v>
       </c>
       <c r="O95">
-        <v>-1.846825664000001</v>
+        <v>-1.891114112000001</v>
       </c>
       <c r="P95">
-        <v>-5.848281269333338</v>
+        <v>-5.988528021333337</v>
       </c>
       <c r="Q95">
-        <v>4.151718730666662</v>
+        <v>4.011471978666663</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6512151868961791</v>
+        <v>0.7521177180455425</v>
       </c>
       <c r="T95">
-        <v>8.33376792891892</v>
+        <v>9.722729250405409</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1323872492992216</v>
+        <v>0.1309788743066767</v>
       </c>
       <c r="W95">
-        <v>0.1742166403407163</v>
+        <v>0.1744994420392193</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5516135387467564</v>
+        <v>0.5457453096111528</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2091565385995987</v>
+        <v>0.2107065385995987</v>
       </c>
       <c r="C96">
-        <v>-42.76155874740039</v>
+        <v>-43.95205870733043</v>
       </c>
       <c r="D96">
-        <v>35.48444125259962</v>
+        <v>35.21294129266958</v>
       </c>
       <c r="E96">
-        <v>34.58600000000001</v>
+        <v>35.505</v>
       </c>
       <c r="F96">
-        <v>86.38600000000001</v>
+        <v>87.30500000000001</v>
       </c>
       <c r="G96">
         <v>8.140000000000001</v>
@@ -9159,37 +9159,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M96">
-        <v>17.3463088</v>
+        <v>17.530844</v>
       </c>
       <c r="N96">
-        <v>-7.879642133333338</v>
+        <v>-8.064177333333337</v>
       </c>
       <c r="O96">
-        <v>-1.891114112000001</v>
+        <v>-1.935402560000001</v>
       </c>
       <c r="P96">
-        <v>-5.988528021333337</v>
+        <v>-6.128774773333336</v>
       </c>
       <c r="Q96">
-        <v>4.011471978666663</v>
+        <v>3.871225226666664</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7521177180455425</v>
+        <v>0.8933812616546514</v>
       </c>
       <c r="T96">
-        <v>9.722729250405409</v>
+        <v>11.6672751004865</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1309788743066767</v>
+        <v>0.1296001493139748</v>
       </c>
       <c r="W96">
-        <v>0.1744994420392193</v>
+        <v>0.1747762900177539</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5457453096111528</v>
+        <v>0.5400006221415616</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2107065385995987</v>
+        <v>0.2122565385995987</v>
       </c>
       <c r="C97">
-        <v>-43.95205870733043</v>
+        <v>-45.13843559144469</v>
       </c>
       <c r="D97">
-        <v>35.21294129266958</v>
+        <v>34.94556440855533</v>
       </c>
       <c r="E97">
-        <v>35.505</v>
+        <v>36.42400000000001</v>
       </c>
       <c r="F97">
-        <v>87.30500000000001</v>
+        <v>88.22400000000002</v>
       </c>
       <c r="G97">
         <v>8.140000000000001</v>
@@ -9241,37 +9241,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M97">
-        <v>17.530844</v>
+        <v>17.7153792</v>
       </c>
       <c r="N97">
-        <v>-8.064177333333337</v>
+        <v>-8.24871253333334</v>
       </c>
       <c r="O97">
-        <v>-1.935402560000001</v>
+        <v>-1.979691008000001</v>
       </c>
       <c r="P97">
-        <v>-6.128774773333336</v>
+        <v>-6.269021525333338</v>
       </c>
       <c r="Q97">
-        <v>3.871225226666664</v>
+        <v>3.730978474666662</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8933812616546514</v>
+        <v>1.105276577068315</v>
       </c>
       <c r="T97">
-        <v>11.6672751004865</v>
+        <v>14.58409387560813</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1296001493139748</v>
+        <v>0.1282501477586209</v>
       </c>
       <c r="W97">
-        <v>0.1747762900177539</v>
+        <v>0.1750473703300689</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5400006221415616</v>
+        <v>0.5343756156609203</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2122565385995987</v>
+        <v>0.2138065385995987</v>
       </c>
       <c r="C98">
-        <v>-45.13843559144468</v>
+        <v>-46.32078261326725</v>
       </c>
       <c r="D98">
-        <v>34.94556440855533</v>
+        <v>34.68221738673275</v>
       </c>
       <c r="E98">
-        <v>36.424</v>
+        <v>37.343</v>
       </c>
       <c r="F98">
-        <v>88.224</v>
+        <v>89.143</v>
       </c>
       <c r="G98">
         <v>8.140000000000001</v>
@@ -9323,37 +9323,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M98">
-        <v>17.7153792</v>
+        <v>17.8999144</v>
       </c>
       <c r="N98">
-        <v>-8.248712533333336</v>
+        <v>-8.433247733333335</v>
       </c>
       <c r="O98">
-        <v>-1.979691008000001</v>
+        <v>-2.023979456</v>
       </c>
       <c r="P98">
-        <v>-6.269021525333335</v>
+        <v>-6.409268277333335</v>
       </c>
       <c r="Q98">
-        <v>3.730978474666665</v>
+        <v>3.590731722666665</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.105276577068312</v>
+        <v>1.458435436091083</v>
       </c>
       <c r="T98">
-        <v>14.58409387560809</v>
+        <v>19.44545850081079</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1282501477586209</v>
+        <v>0.1269279812868825</v>
       </c>
       <c r="W98">
-        <v>0.1750473703300689</v>
+        <v>0.175312861357594</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5343756156609205</v>
+        <v>0.528866588695344</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2138065385995987</v>
+        <v>0.2153565385995987</v>
       </c>
       <c r="C99">
-        <v>-46.32078261326725</v>
+        <v>-47.4991901975392</v>
       </c>
       <c r="D99">
-        <v>34.68221738673275</v>
+        <v>34.4228098024608</v>
       </c>
       <c r="E99">
-        <v>37.343</v>
+        <v>38.26199999999999</v>
       </c>
       <c r="F99">
-        <v>89.143</v>
+        <v>90.062</v>
       </c>
       <c r="G99">
         <v>8.140000000000001</v>
@@ -9405,37 +9405,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M99">
-        <v>17.8999144</v>
+        <v>18.0844496</v>
       </c>
       <c r="N99">
-        <v>-8.433247733333335</v>
+        <v>-8.617782933333334</v>
       </c>
       <c r="O99">
-        <v>-2.023979456</v>
+        <v>-2.068267904</v>
       </c>
       <c r="P99">
-        <v>-6.409268277333335</v>
+        <v>-6.549515029333334</v>
       </c>
       <c r="Q99">
-        <v>3.590731722666665</v>
+        <v>3.450484970666666</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.458435436091083</v>
+        <v>2.164753154136624</v>
       </c>
       <c r="T99">
-        <v>19.44545850081079</v>
+        <v>29.16818775121618</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1269279812868825</v>
+        <v>0.1256327978043633</v>
       </c>
       <c r="W99">
-        <v>0.175312861357594</v>
+        <v>0.1755729342008839</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.528866588695344</v>
+        <v>0.5234699908515139</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2153565385995987</v>
+        <v>0.2169065385995987</v>
       </c>
       <c r="C100">
-        <v>-47.4991901975392</v>
+        <v>-48.67374608373851</v>
       </c>
       <c r="D100">
-        <v>34.4228098024608</v>
+        <v>34.16725391626149</v>
       </c>
       <c r="E100">
-        <v>38.26199999999999</v>
+        <v>39.181</v>
       </c>
       <c r="F100">
-        <v>90.062</v>
+        <v>90.98100000000001</v>
       </c>
       <c r="G100">
         <v>8.140000000000001</v>
@@ -9487,37 +9487,37 @@
         <v>9.466666666666665</v>
       </c>
       <c r="M100">
-        <v>18.0844496</v>
+        <v>18.2689848</v>
       </c>
       <c r="N100">
-        <v>-8.617782933333334</v>
+        <v>-8.802318133333337</v>
       </c>
       <c r="O100">
-        <v>-2.068267904</v>
+        <v>-2.112556352000001</v>
       </c>
       <c r="P100">
-        <v>-6.549515029333334</v>
+        <v>-6.689761781333337</v>
       </c>
       <c r="Q100">
-        <v>3.450484970666666</v>
+        <v>3.310238218666663</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.164753154136624</v>
+        <v>4.283706308273246</v>
       </c>
       <c r="T100">
-        <v>29.16818775121618</v>
+        <v>58.33637550243235</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1256327978043633</v>
+        <v>0.1243637796447233</v>
       </c>
       <c r="W100">
-        <v>0.1755729342008839</v>
+        <v>0.1758277530473396</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5234699908515139</v>
+        <v>0.518182415186347</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2169065385995987</v>
-      </c>
-      <c r="C101">
-        <v>-48.67374608373851</v>
-      </c>
-      <c r="D101">
-        <v>34.16725391626149</v>
-      </c>
-      <c r="E101">
-        <v>39.181</v>
-      </c>
-      <c r="F101">
-        <v>90.98100000000001</v>
-      </c>
-      <c r="G101">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="H101">
-        <v>40.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>19.46666666666667</v>
-      </c>
-      <c r="K101">
-        <v>10</v>
-      </c>
-      <c r="L101">
-        <v>9.466666666666665</v>
-      </c>
-      <c r="M101">
-        <v>18.2689848</v>
-      </c>
-      <c r="N101">
-        <v>-8.802318133333337</v>
-      </c>
-      <c r="O101">
-        <v>-2.112556352000001</v>
-      </c>
-      <c r="P101">
-        <v>-6.689761781333337</v>
-      </c>
-      <c r="Q101">
-        <v>3.310238218666663</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.283706308273246</v>
-      </c>
-      <c r="T101">
-        <v>58.33637550243235</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1243637796447233</v>
-      </c>
-      <c r="W101">
-        <v>0.1758277530473396</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.518182415186347</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
